--- a/docs/data/jp/xlsx/6861.xlsx
+++ b/docs/data/jp/xlsx/6861.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC133"/>
+  <dimension ref="A1:AC140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4175,10 +4178,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>77270</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4213,7 +4218,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>243207684</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5412,7 +5419,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5655,995 +5662,987 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S79" s="17">
+        <f>IF(OR(S78="",R78=""),"",IF(R78&lt;=0,"",IFERROR(S78/R78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>39831</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>42467</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>42282</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>40202</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>45412</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>49010</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>48769</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>28253</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>51866</v>
       </c>
-      <c r="S79" s="22" t="n">
+      <c r="S80" s="22" t="n">
         <v>2048</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>10573</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>45309</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>40202</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>28253</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>207391</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>225861</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>217357</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>151896</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>215664</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>235214</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>240535</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>196287</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>294755</v>
       </c>
-      <c r="S80" s="12" t="n">
+      <c r="S81" s="12" t="n">
         <v>-9246</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>63984</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>169924</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>151896</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>196287</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>83986</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>85301</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>84288</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>53916</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>86363</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>92335</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>62893</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>107679</v>
-      </c>
-      <c r="S81" s="22" t="n">
-        <v>16406</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>14970</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>30525</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>53916</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>62893</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>123405</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>140560</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>133068</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>97981</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>129301</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>142878</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>144202</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>133394</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>187076</v>
-      </c>
-      <c r="S82" s="12" t="n">
-        <v>-25653</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>49014</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>139399</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>97981</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>133394</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S82" s="17">
+        <f>IF(OR(S81="",R81=""),"",IF(R81&lt;=0,"",IFERROR(S81/R81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>1677</v>
+        <v>83986</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>2228</v>
+        <v>85301</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>2176</v>
+        <v>84288</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-723</v>
+        <v>53916</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>3089</v>
+        <v>86363</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>3991</v>
+        <v>92335</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>3986</v>
+        <v>96334</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-2098</v>
+        <v>62893</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>6091</v>
+        <v>107679</v>
       </c>
       <c r="S83" s="22" t="n">
-        <v>342</v>
+        <v>16406</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>-578</v>
+        <v>14970</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>-1647</v>
+        <v>30525</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>-723</v>
+        <v>53916</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>-2098</v>
+        <v>62893</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>1012</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>1455</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>1453</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>1451</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>1121</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>1776</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>1869</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>543</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>1295</v>
-      </c>
-      <c r="S84" s="22" t="n">
-        <v>794</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>773</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>1477</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>1451</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>543</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>123405</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>140560</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>133068</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>97981</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>129301</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>142878</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>144202</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>133394</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>187076</v>
+      </c>
+      <c r="S84" s="12" t="n">
+        <v>-25653</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>49014</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>139399</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>97981</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>133394</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>5283</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>-5283</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>2043</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>10790</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>1644</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>8512</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>-10156</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>2243</v>
-      </c>
-      <c r="S85" s="22" t="n">
-        <v>1173</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>1579</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>-4158</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>10790</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>-10156</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="S85" s="17">
+        <f>IF(OR(S84="",S78=""),"",IF(S78&lt;=0,"",IFERROR(S84/S78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>잡이익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>111</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>82</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>1326</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>-114</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>172</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>1155</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>106</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>609</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>168</v>
-      </c>
-      <c r="S86" s="22" t="n">
-        <v>81</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>185</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>322</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>-114</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>609</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S86" s="17">
+        <f>IF(OR(S84="",R84=""),"",IF(R84&lt;=0,"",IFERROR(S84/R84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>8084</v>
+        <v>1677</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>-1518</v>
+        <v>2228</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>6998</v>
+        <v>2176</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>11405</v>
+        <v>-723</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>4383</v>
+        <v>3089</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>8566</v>
+        <v>3991</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>14473</v>
+        <v>3986</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>-11102</v>
+        <v>-2098</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>9798</v>
+        <v>6091</v>
       </c>
       <c r="S87" s="22" t="n">
-        <v>2391</v>
+        <v>342</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>1957</v>
+        <v>-578</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>-4005</v>
+        <v>-1647</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>11405</v>
+        <v>-723</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>-11102</v>
+        <v>-2098</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>0</v>
+        <v>1012</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>4705</v>
+        <v>1455</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>1453</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>1451</v>
       </c>
       <c r="G88" s="22" t="n">
-        <v>2070</v>
+        <v>1121</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>-2070</v>
+        <v>1776</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>1869</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>543</v>
       </c>
       <c r="K88" s="22" t="n">
-        <v>0</v>
+        <v>1295</v>
+      </c>
+      <c r="S88" s="22" t="n">
+        <v>794</v>
+      </c>
+      <c r="T88" s="22" t="n">
+        <v>773</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>1477</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>1451</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>543</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>잡손실</t>
+          <t>외환차익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>44</v>
+        <v>5283</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>64</v>
+        <v>-5283</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>153</v>
+        <v>2043</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>427</v>
+        <v>10790</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>47</v>
+        <v>1644</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>60</v>
+        <v>8512</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>675</v>
+        <v>-10156</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>81</v>
+        <v>2243</v>
       </c>
       <c r="S89" s="22" t="n">
-        <v>-8</v>
+        <v>1173</v>
       </c>
       <c r="T89" s="22" t="n">
-        <v>25</v>
+        <v>1579</v>
       </c>
       <c r="U89" s="22" t="n">
-        <v>125</v>
+        <v>-4158</v>
       </c>
       <c r="V89" s="22" t="n">
-        <v>427</v>
+        <v>10790</v>
       </c>
       <c r="W89" s="22" t="n">
-        <v>675</v>
+        <v>-10156</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>잡이익</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="D90" s="22" t="n">
-        <v>4770</v>
+        <v>82</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>-4553</v>
+        <v>1326</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>427</v>
+        <v>-114</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>2153</v>
+        <v>172</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>-2024</v>
+        <v>1155</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>4896</v>
+        <v>609</v>
       </c>
       <c r="K90" s="22" t="n">
+        <v>168</v>
+      </c>
+      <c r="S90" s="22" t="n">
         <v>81</v>
       </c>
-      <c r="S90" s="22" t="n">
-        <v>-8</v>
-      </c>
       <c r="T90" s="22" t="n">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>125</v>
+        <v>322</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>427</v>
+        <v>-114</v>
       </c>
       <c r="W90" s="22" t="n">
-        <v>4896</v>
+        <v>609</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C91" s="12" t="n">
-        <v>131444</v>
-      </c>
-      <c r="D91" s="12" t="n">
-        <v>134273</v>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v>144619</v>
-      </c>
-      <c r="F91" s="12" t="n">
-        <v>108959</v>
-      </c>
-      <c r="G91" s="12" t="n">
-        <v>131532</v>
-      </c>
-      <c r="H91" s="12" t="n">
-        <v>153468</v>
-      </c>
-      <c r="I91" s="12" t="n">
-        <v>158614</v>
-      </c>
-      <c r="J91" s="12" t="n">
-        <v>117396</v>
-      </c>
-      <c r="K91" s="12" t="n">
-        <v>196793</v>
-      </c>
-      <c r="S91" s="12" t="n">
-        <v>-23254</v>
-      </c>
-      <c r="T91" s="12" t="n">
-        <v>50946</v>
-      </c>
-      <c r="U91" s="12" t="n">
-        <v>135270</v>
-      </c>
-      <c r="V91" s="12" t="n">
-        <v>108959</v>
-      </c>
-      <c r="W91" s="12" t="n">
-        <v>117396</v>
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="n">
+        <v>8084</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>-1518</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>6998</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>11405</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>4383</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>8566</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>14473</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>-11102</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>9798</v>
+      </c>
+      <c r="S91" s="22" t="n">
+        <v>2391</v>
+      </c>
+      <c r="T91" s="22" t="n">
+        <v>1957</v>
+      </c>
+      <c r="U91" s="22" t="n">
+        <v>-4005</v>
+      </c>
+      <c r="V91" s="22" t="n">
+        <v>11405</v>
+      </c>
+      <c r="W91" s="22" t="n">
+        <v>-11102</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="n">
-        <v>131444</v>
-      </c>
-      <c r="D92" s="12" t="n">
-        <v>134273</v>
-      </c>
-      <c r="E92" s="12" t="n">
-        <v>144619</v>
-      </c>
-      <c r="F92" s="12" t="n">
-        <v>108959</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>131532</v>
-      </c>
-      <c r="H92" s="12" t="n">
-        <v>153468</v>
-      </c>
-      <c r="I92" s="12" t="n">
-        <v>158614</v>
-      </c>
-      <c r="J92" s="12" t="n">
-        <v>117396</v>
-      </c>
-      <c r="K92" s="12" t="n">
-        <v>196793</v>
-      </c>
-      <c r="S92" s="12" t="n">
-        <v>-23254</v>
-      </c>
-      <c r="T92" s="12" t="n">
-        <v>50946</v>
-      </c>
-      <c r="U92" s="12" t="n">
-        <v>135270</v>
-      </c>
-      <c r="V92" s="12" t="n">
-        <v>108959</v>
-      </c>
-      <c r="W92" s="12" t="n">
-        <v>117396</v>
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>4705</v>
+      </c>
+      <c r="G92" s="22" t="n">
+        <v>2070</v>
+      </c>
+      <c r="H92" s="22" t="n">
+        <v>-2070</v>
+      </c>
+      <c r="K92" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>법인세 등</t>
+          <t>잡손실</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>37909</v>
+        <v>44</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>38088</v>
+        <v>64</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>42574</v>
+        <v>153</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>31082</v>
+        <v>427</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>39415</v>
+        <v>82</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>45625</v>
+        <v>47</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>47406</v>
+        <v>60</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>29907</v>
+        <v>675</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>57660</v>
+        <v>81</v>
       </c>
       <c r="S93" s="22" t="n">
-        <v>-2138</v>
+        <v>-8</v>
       </c>
       <c r="T93" s="22" t="n">
-        <v>15609</v>
+        <v>25</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>38733</v>
+        <v>125</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>31082</v>
+        <v>427</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>29907</v>
+        <v>675</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="n">
-        <v>93534</v>
-      </c>
-      <c r="D94" s="12" t="n">
-        <v>96186</v>
-      </c>
-      <c r="E94" s="12" t="n">
-        <v>102045</v>
-      </c>
-      <c r="F94" s="12" t="n">
-        <v>77877</v>
-      </c>
-      <c r="G94" s="12" t="n">
-        <v>92116</v>
-      </c>
-      <c r="H94" s="12" t="n">
-        <v>107843</v>
-      </c>
-      <c r="I94" s="12" t="n">
-        <v>111208</v>
-      </c>
-      <c r="J94" s="12" t="n">
-        <v>87489</v>
-      </c>
-      <c r="K94" s="12" t="n">
-        <v>139133</v>
-      </c>
-      <c r="S94" s="12" t="n">
-        <v>-21116</v>
-      </c>
-      <c r="T94" s="12" t="n">
-        <v>35338</v>
-      </c>
-      <c r="U94" s="12" t="n">
-        <v>96537</v>
-      </c>
-      <c r="V94" s="12" t="n">
-        <v>77877</v>
-      </c>
-      <c r="W94" s="12" t="n">
-        <v>87489</v>
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>4770</v>
+      </c>
+      <c r="E94" s="22" t="n">
+        <v>-4553</v>
+      </c>
+      <c r="F94" s="22" t="n">
+        <v>427</v>
+      </c>
+      <c r="G94" s="22" t="n">
+        <v>2153</v>
+      </c>
+      <c r="H94" s="22" t="n">
+        <v>-2024</v>
+      </c>
+      <c r="I94" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="J94" s="22" t="n">
+        <v>4896</v>
+      </c>
+      <c r="K94" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="S94" s="22" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T94" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>125</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>427</v>
+      </c>
+      <c r="W94" s="22" t="n">
+        <v>4896</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>경상이익</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>93534</v>
+        <v>131444</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>96186</v>
+        <v>134273</v>
       </c>
       <c r="E95" s="12" t="n">
-        <v>102045</v>
+        <v>144619</v>
       </c>
       <c r="F95" s="12" t="n">
-        <v>77877</v>
+        <v>108959</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>92116</v>
+        <v>131532</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>107843</v>
+        <v>153468</v>
       </c>
       <c r="I95" s="12" t="n">
-        <v>111208</v>
+        <v>158614</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>87489</v>
+        <v>117396</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>139133</v>
+        <v>196793</v>
       </c>
       <c r="S95" s="12" t="n">
-        <v>-21116</v>
+        <v>-23254</v>
       </c>
       <c r="T95" s="12" t="n">
-        <v>35338</v>
+        <v>50946</v>
       </c>
       <c r="U95" s="12" t="n">
-        <v>96537</v>
+        <v>135270</v>
       </c>
       <c r="V95" s="12" t="n">
-        <v>77877</v>
+        <v>108959</v>
       </c>
       <c r="W95" s="12" t="n">
-        <v>87489</v>
+        <v>117396</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G96" s="17">
+        <f>IF(OR(G95="",C95=""),"",IF(C95&lt;=0,"",IFERROR(G95/C95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H96" s="17">
+        <f>IF(OR(H95="",D95=""),"",IF(D95&lt;=0,"",IFERROR(H95/D95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I96" s="17">
+        <f>IF(OR(I95="",E95=""),"",IF(E95&lt;=0,"",IFERROR(I95/E95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J96" s="17">
+        <f>IF(OR(J95="",F95=""),"",IF(F95&lt;=0,"",IFERROR(J95/F95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K96" s="17">
+        <f>IF(OR(K95="",G95=""),"",IF(G95&lt;=0,"",IFERROR(K95/G95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S96" s="17">
+        <f>IF(OR(S95="",R95=""),"",IF(R95&lt;=0,"",IFERROR(S95/R95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T96" s="17">
+        <f>IF(OR(T95="",S95=""),"",IF(S95&lt;=0,"",IFERROR(T95/S95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U96" s="17">
+        <f>IF(OR(U95="",T95=""),"",IF(T95&lt;=0,"",IFERROR(U95/T95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V96" s="17">
+        <f>IF(OR(V95="",U95=""),"",IF(U95&lt;=0,"",IFERROR(V95/U95-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W96" s="17">
+        <f>IF(OR(W95="",V95=""),"",IF(V95&lt;=0,"",IFERROR(W95/V95-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="18" t="inlineStr">
-        <is>
-          <t>포괄손익 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B97" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 3개월 단독</t>
-        </is>
-      </c>
-      <c r="C97" s="18" t="n"/>
-      <c r="D97" s="18" t="n"/>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
-      <c r="K97" s="18" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="18" t="n"/>
-      <c r="N97" s="18" t="n"/>
-      <c r="O97" s="18" t="n"/>
-      <c r="P97" s="18" t="n"/>
-      <c r="Q97" s="18" t="n"/>
-      <c r="R97" s="18" t="n"/>
-      <c r="S97" s="18" t="n"/>
-      <c r="T97" s="18" t="n"/>
-      <c r="U97" s="18" t="n"/>
-      <c r="V97" s="18" t="n"/>
-      <c r="W97" s="18" t="n"/>
-      <c r="X97" s="18" t="n"/>
-      <c r="Y97" s="18" t="n"/>
-      <c r="Z97" s="18" t="n"/>
-      <c r="AA97" s="18" t="n"/>
-      <c r="AB97" s="18" t="n"/>
-      <c r="AC97" s="18" t="n"/>
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>131444</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>134273</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>144619</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>108959</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>131532</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>153468</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>158614</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>117396</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>196793</v>
+      </c>
+      <c r="S97" s="12" t="n">
+        <v>-23254</v>
+      </c>
+      <c r="T97" s="12" t="n">
+        <v>50946</v>
+      </c>
+      <c r="U97" s="12" t="n">
+        <v>135270</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>108959</v>
+      </c>
+      <c r="W97" s="12" t="n">
+        <v>117396</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
-        <is>
-          <t>2027.2Q</t>
-        </is>
-      </c>
-      <c r="M98" s="5" t="inlineStr">
-        <is>
-          <t>2027.3Q</t>
-        </is>
-      </c>
-      <c r="N98" s="5" t="inlineStr">
-        <is>
-          <t>2027.4Q</t>
-        </is>
-      </c>
-      <c r="O98" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="P98" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="Q98" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="R98" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="S98" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="T98" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U98" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V98" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="W98" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="X98" s="5" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="Y98" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="Z98" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AA98" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AB98" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
-      </c>
-      <c r="AC98" s="5" t="inlineStr">
-        <is>
-          <t>2032(MW)</t>
-        </is>
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n">
+        <v>37909</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>38088</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>42574</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>31082</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>39415</v>
+      </c>
+      <c r="H98" s="22" t="n">
+        <v>45625</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>47406</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>29907</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>57660</v>
+      </c>
+      <c r="S98" s="22" t="n">
+        <v>-2138</v>
+      </c>
+      <c r="T98" s="22" t="n">
+        <v>15609</v>
+      </c>
+      <c r="U98" s="22" t="n">
+        <v>38733</v>
+      </c>
+      <c r="V98" s="22" t="n">
+        <v>31082</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>29907</v>
       </c>
     </row>
     <row r="99">
@@ -6696,1548 +6695,1936 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="20" t="inlineStr">
+      <c r="A100" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G100" s="17">
+        <f>IF(OR(G99="",C99=""),"",IF(C99&lt;=0,"",IFERROR(G99/C99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H100" s="17">
+        <f>IF(OR(H99="",D99=""),"",IF(D99&lt;=0,"",IFERROR(H99/D99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I100" s="17">
+        <f>IF(OR(I99="",E99=""),"",IF(E99&lt;=0,"",IFERROR(I99/E99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J100" s="17">
+        <f>IF(OR(J99="",F99=""),"",IF(F99&lt;=0,"",IFERROR(J99/F99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF(OR(K99="",G99=""),"",IF(G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S100" s="17">
+        <f>IF(OR(S99="",R99=""),"",IF(R99&lt;=0,"",IFERROR(S99/R99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T100" s="17">
+        <f>IF(OR(T99="",S99=""),"",IF(S99&lt;=0,"",IFERROR(T99/S99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U100" s="17">
+        <f>IF(OR(U99="",T99=""),"",IF(T99&lt;=0,"",IFERROR(U99/T99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V100" s="17">
+        <f>IF(OR(V99="",U99=""),"",IF(U99&lt;=0,"",IFERROR(V99/U99-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W100" s="17">
+        <f>IF(OR(W99="",V99=""),"",IF(V99&lt;=0,"",IFERROR(W99/V99-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>93534</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>96186</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>102045</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>77877</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>92116</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>107843</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>111208</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>87489</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>139133</v>
+      </c>
+      <c r="S101" s="12" t="n">
+        <v>-21116</v>
+      </c>
+      <c r="T101" s="12" t="n">
+        <v>35338</v>
+      </c>
+      <c r="U101" s="12" t="n">
+        <v>96537</v>
+      </c>
+      <c r="V101" s="12" t="n">
+        <v>77877</v>
+      </c>
+      <c r="W101" s="12" t="n">
+        <v>87489</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G102" s="17">
+        <f>IF(OR(G101="",C101=""),"",IF(C101&lt;=0,"",IFERROR(G101/C101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H102" s="17">
+        <f>IF(OR(H101="",D101=""),"",IF(D101&lt;=0,"",IFERROR(H101/D101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I102" s="17">
+        <f>IF(OR(I101="",E101=""),"",IF(E101&lt;=0,"",IFERROR(I101/E101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J102" s="17">
+        <f>IF(OR(J101="",F101=""),"",IF(F101&lt;=0,"",IFERROR(J101/F101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF(OR(K101="",G101=""),"",IF(G101&lt;=0,"",IFERROR(K101/G101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="S102" s="17">
+        <f>IF(OR(S101="",R101=""),"",IF(R101&lt;=0,"",IFERROR(S101/R101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T102" s="17">
+        <f>IF(OR(T101="",S101=""),"",IF(S101&lt;=0,"",IFERROR(T101/S101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U102" s="17">
+        <f>IF(OR(U101="",T101=""),"",IF(T101&lt;=0,"",IFERROR(U101/T101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V102" s="17">
+        <f>IF(OR(V101="",U101=""),"",IF(U101&lt;=0,"",IFERROR(V101/U101-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W102" s="17">
+        <f>IF(OR(W101="",V101=""),"",IF(V101&lt;=0,"",IFERROR(W101/V101-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>포괄손익 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B104" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 3개월 단독</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="n"/>
+      <c r="D104" s="18" t="n"/>
+      <c r="E104" s="18" t="n"/>
+      <c r="F104" s="18" t="n"/>
+      <c r="G104" s="18" t="n"/>
+      <c r="H104" s="18" t="n"/>
+      <c r="I104" s="18" t="n"/>
+      <c r="J104" s="18" t="n"/>
+      <c r="K104" s="18" t="n"/>
+      <c r="L104" s="18" t="n"/>
+      <c r="M104" s="18" t="n"/>
+      <c r="N104" s="18" t="n"/>
+      <c r="O104" s="18" t="n"/>
+      <c r="P104" s="18" t="n"/>
+      <c r="Q104" s="18" t="n"/>
+      <c r="R104" s="18" t="n"/>
+      <c r="S104" s="18" t="n"/>
+      <c r="T104" s="18" t="n"/>
+      <c r="U104" s="18" t="n"/>
+      <c r="V104" s="18" t="n"/>
+      <c r="W104" s="18" t="n"/>
+      <c r="X104" s="18" t="n"/>
+      <c r="Y104" s="18" t="n"/>
+      <c r="Z104" s="18" t="n"/>
+      <c r="AA104" s="18" t="n"/>
+      <c r="AB104" s="18" t="n"/>
+      <c r="AC104" s="18" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="H105" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>2027.2Q</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
+          <t>2027.3Q</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>2027.4Q</t>
+        </is>
+      </c>
+      <c r="O105" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="P105" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q105" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="R105" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="S105" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="T105" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U105" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V105" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W105" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="X105" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="Y105" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="Z105" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AA105" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AB105" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+      <c r="AC105" s="5" t="inlineStr">
+        <is>
+          <t>2032(MW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>93534</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>96186</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>102045</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>77877</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>92116</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>107843</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>111208</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>87489</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>139133</v>
+      </c>
+      <c r="S106" s="12" t="n">
+        <v>-21116</v>
+      </c>
+      <c r="T106" s="12" t="n">
+        <v>35338</v>
+      </c>
+      <c r="U106" s="12" t="n">
+        <v>96537</v>
+      </c>
+      <c r="V106" s="12" t="n">
+        <v>77877</v>
+      </c>
+      <c r="W106" s="12" t="n">
+        <v>87489</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C100" s="22" t="n">
+      <c r="C107" s="22" t="n">
         <v>-344</v>
       </c>
-      <c r="D100" s="22" t="n">
+      <c r="D107" s="22" t="n">
         <v>-809</v>
       </c>
-      <c r="E100" s="22" t="n">
+      <c r="E107" s="22" t="n">
         <v>-2350</v>
       </c>
-      <c r="F100" s="22" t="n">
+      <c r="F107" s="22" t="n">
         <v>1485</v>
       </c>
-      <c r="G100" s="22" t="n">
+      <c r="G107" s="22" t="n">
         <v>4228</v>
       </c>
-      <c r="H100" s="22" t="n">
+      <c r="H107" s="22" t="n">
         <v>-3114</v>
       </c>
-      <c r="I100" s="22" t="n">
+      <c r="I107" s="22" t="n">
         <v>-3534</v>
       </c>
-      <c r="J100" s="22" t="n">
+      <c r="J107" s="22" t="n">
         <v>-5939</v>
       </c>
-      <c r="K100" s="22" t="n">
+      <c r="K107" s="22" t="n">
         <v>-543</v>
       </c>
-      <c r="S100" s="22" t="n">
+      <c r="S107" s="22" t="n">
         <v>3438</v>
       </c>
-      <c r="T100" s="22" t="n">
+      <c r="T107" s="22" t="n">
         <v>612</v>
       </c>
-      <c r="U100" s="22" t="n">
+      <c r="U107" s="22" t="n">
         <v>-833</v>
       </c>
-      <c r="V100" s="22" t="n">
+      <c r="V107" s="22" t="n">
         <v>1485</v>
       </c>
-      <c r="W100" s="22" t="n">
+      <c r="W107" s="22" t="n">
         <v>-5939</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
         <is>
           <t>해외사업환산조정</t>
         </is>
       </c>
-      <c r="C101" s="22" t="n">
+      <c r="C108" s="22" t="n">
         <v>8270</v>
       </c>
-      <c r="D101" s="22" t="n">
+      <c r="D108" s="22" t="n">
         <v>-18112</v>
       </c>
-      <c r="E101" s="22" t="n">
+      <c r="E108" s="22" t="n">
         <v>5165</v>
       </c>
-      <c r="F101" s="22" t="n">
+      <c r="F108" s="22" t="n">
         <v>24428</v>
       </c>
-      <c r="G101" s="22" t="n">
+      <c r="G108" s="22" t="n">
         <v>425</v>
       </c>
-      <c r="H101" s="22" t="n">
+      <c r="H108" s="22" t="n">
         <v>8040</v>
       </c>
-      <c r="I101" s="22" t="n">
+      <c r="I108" s="22" t="n">
         <v>18799</v>
       </c>
-      <c r="J101" s="22" t="n">
+      <c r="J108" s="22" t="n">
         <v>-36435</v>
       </c>
-      <c r="K101" s="22" t="n">
+      <c r="K108" s="22" t="n">
         <v>5363</v>
       </c>
-      <c r="S101" s="22" t="n">
+      <c r="S108" s="22" t="n">
         <v>-3023</v>
       </c>
-      <c r="T101" s="22" t="n">
+      <c r="T108" s="22" t="n">
         <v>-10048</v>
       </c>
-      <c r="U101" s="22" t="n">
+      <c r="U108" s="22" t="n">
         <v>1191</v>
       </c>
-      <c r="V101" s="22" t="n">
+      <c r="V108" s="22" t="n">
         <v>24428</v>
       </c>
-      <c r="W101" s="22" t="n">
+      <c r="W108" s="22" t="n">
         <v>-36435</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="20" t="inlineStr">
         <is>
           <t>지분법 적용회사 지분 해당액</t>
         </is>
       </c>
-      <c r="C102" s="22" t="n">
+      <c r="C109" s="22" t="n">
         <v>55</v>
       </c>
-      <c r="D102" s="22" t="n">
+      <c r="D109" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="E102" s="22" t="n">
+      <c r="E109" s="22" t="n">
         <v>-52</v>
       </c>
-      <c r="F102" s="22" t="n">
+      <c r="F109" s="22" t="n">
         <v>-64</v>
       </c>
-      <c r="G102" s="22" t="n">
+      <c r="G109" s="22" t="n">
         <v>-27</v>
       </c>
-      <c r="H102" s="22" t="n">
+      <c r="H109" s="22" t="n">
         <v>-18</v>
       </c>
-      <c r="I102" s="22" t="n">
+      <c r="I109" s="22" t="n">
         <v>18</v>
       </c>
-      <c r="J102" s="22" t="n">
+      <c r="J109" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="K102" s="22" t="n">
+      <c r="K109" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="S102" s="22" t="n">
+      <c r="S109" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="T102" s="22" t="n">
+      <c r="T109" s="22" t="n">
         <v>-4</v>
       </c>
-      <c r="U102" s="22" t="n">
+      <c r="U109" s="22" t="n">
         <v>-6</v>
       </c>
-      <c r="V102" s="22" t="n">
+      <c r="V109" s="22" t="n">
         <v>-64</v>
       </c>
-      <c r="W102" s="22" t="n">
+      <c r="W109" s="22" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="n">
-        <v>7981</v>
-      </c>
-      <c r="D103" s="22" t="n">
-        <v>-18896</v>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>2764</v>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>25848</v>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>4626</v>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>4908</v>
-      </c>
-      <c r="I103" s="22" t="n">
-        <v>15282</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>-42273</v>
-      </c>
-      <c r="K103" s="22" t="n">
-        <v>4833</v>
-      </c>
-      <c r="S103" s="22" t="n">
-        <v>431</v>
-      </c>
-      <c r="T103" s="22" t="n">
-        <v>-9441</v>
-      </c>
-      <c r="U103" s="22" t="n">
-        <v>354</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>25848</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>-42273</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n">
-        <v>101516</v>
-      </c>
-      <c r="D104" s="12" t="n">
-        <v>77289</v>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>104809</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>103725</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>96743</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>112751</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>126489</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>45216</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>143967</v>
-      </c>
-      <c r="S104" s="12" t="n">
-        <v>-20685</v>
-      </c>
-      <c r="T104" s="12" t="n">
-        <v>25896</v>
-      </c>
-      <c r="U104" s="12" t="n">
-        <v>96891</v>
-      </c>
-      <c r="V104" s="12" t="n">
-        <v>103725</v>
-      </c>
-      <c r="W104" s="12" t="n">
-        <v>45216</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
-        <is>
-          <t>지배주주 포괄이익</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>101516</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>77289</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>104809</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>103725</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>96743</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>112751</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>126489</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>45216</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>143967</v>
-      </c>
-      <c r="S105" s="12" t="n">
-        <v>-20685</v>
-      </c>
-      <c r="T105" s="12" t="n">
-        <v>25896</v>
-      </c>
-      <c r="U105" s="12" t="n">
-        <v>96891</v>
-      </c>
-      <c r="V105" s="12" t="n">
-        <v>103725</v>
-      </c>
-      <c r="W105" s="12" t="n">
-        <v>45216</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B107" s="44" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C107" s="18" t="n"/>
-      <c r="D107" s="18" t="n"/>
-      <c r="E107" s="18" t="n"/>
-      <c r="F107" s="18" t="n"/>
-      <c r="G107" s="18" t="n"/>
-      <c r="H107" s="18" t="n"/>
-      <c r="I107" s="18" t="n"/>
-      <c r="J107" s="18" t="n"/>
-      <c r="K107" s="18" t="n"/>
-      <c r="L107" s="18" t="n"/>
-      <c r="M107" s="18" t="n"/>
-      <c r="N107" s="18" t="n"/>
-      <c r="O107" s="18" t="n"/>
-      <c r="P107" s="18" t="n"/>
-      <c r="Q107" s="18" t="n"/>
-      <c r="R107" s="18" t="n"/>
-      <c r="S107" s="18" t="n"/>
-      <c r="T107" s="18" t="n"/>
-      <c r="U107" s="18" t="n"/>
-      <c r="V107" s="18" t="n"/>
-      <c r="W107" s="18" t="n"/>
-      <c r="X107" s="18" t="n"/>
-      <c r="Y107" s="18" t="n"/>
-      <c r="Z107" s="18" t="n"/>
-      <c r="AA107" s="18" t="n"/>
-      <c r="AB107" s="18" t="n"/>
-      <c r="AC107" s="18" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B108" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C108" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="F108" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="G108" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="H108" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>2027.2Q</t>
-        </is>
-      </c>
-      <c r="M108" s="5" t="inlineStr">
-        <is>
-          <t>2027.3Q</t>
-        </is>
-      </c>
-      <c r="N108" s="5" t="inlineStr">
-        <is>
-          <t>2027.4Q</t>
-        </is>
-      </c>
-      <c r="O108" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="P108" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="Q108" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="R108" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="S108" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="T108" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="U108" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="V108" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="W108" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="X108" s="5" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="Y108" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="Z108" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AA108" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AB108" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
-      </c>
-      <c r="AC108" s="5" t="inlineStr">
-        <is>
-          <t>2032(MW)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>519295</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>561010</v>
-      </c>
-      <c r="N109" s="12" t="n">
-        <v>635756</v>
-      </c>
-      <c r="P109" s="12" t="n">
-        <v>298860</v>
-      </c>
-      <c r="Q109" s="12" t="n">
-        <v>319860</v>
-      </c>
-      <c r="R109" s="12" t="n">
-        <v>280253</v>
-      </c>
-      <c r="S109" s="12" t="n">
-        <v>286594</v>
-      </c>
-      <c r="T109" s="12" t="n">
-        <v>431240</v>
-      </c>
-      <c r="U109" s="12" t="n">
-        <v>512830</v>
-      </c>
-      <c r="V109" s="12" t="n">
-        <v>519295</v>
-      </c>
-      <c r="W109" s="12" t="n">
-        <v>561010</v>
-      </c>
-      <c r="X109" s="12" t="n">
-        <v>635756</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>7981</v>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>-18896</v>
+      </c>
+      <c r="E110" s="22" t="n">
+        <v>2764</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>13767</v>
+        <v>25848</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>4626</v>
+      </c>
+      <c r="H110" s="22" t="n">
+        <v>4908</v>
+      </c>
+      <c r="I110" s="22" t="n">
+        <v>15282</v>
       </c>
       <c r="J110" s="22" t="n">
-        <v>15193</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>17227</v>
-      </c>
-      <c r="P110" s="22" t="n">
-        <v>4577</v>
-      </c>
-      <c r="Q110" s="22" t="n">
-        <v>6288</v>
-      </c>
-      <c r="R110" s="22" t="n">
-        <v>7995</v>
+        <v>-42273</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>4833</v>
       </c>
       <c r="S110" s="22" t="n">
-        <v>7555</v>
+        <v>431</v>
       </c>
       <c r="T110" s="22" t="n">
-        <v>8621</v>
+        <v>-9441</v>
       </c>
       <c r="U110" s="22" t="n">
-        <v>11523</v>
+        <v>354</v>
       </c>
       <c r="V110" s="22" t="n">
-        <v>13767</v>
+        <v>25848</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>15193</v>
-      </c>
-      <c r="X110" s="22" t="n">
-        <v>17227</v>
+        <v>-42273</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>-5459</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>-9083</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>-16368</v>
-      </c>
-      <c r="P111" s="22" t="n">
-        <v>-988</v>
-      </c>
-      <c r="Q111" s="22" t="n">
-        <v>-1245</v>
-      </c>
-      <c r="R111" s="22" t="n">
-        <v>-1326</v>
-      </c>
-      <c r="S111" s="22" t="n">
-        <v>-838</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>-646</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>-2129</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>-5459</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-9083</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>-16368</v>
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>101516</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>77289</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>104809</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>103725</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>96743</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>112751</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>126489</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>45216</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>143967</v>
+      </c>
+      <c r="S111" s="12" t="n">
+        <v>-20685</v>
+      </c>
+      <c r="T111" s="12" t="n">
+        <v>25896</v>
+      </c>
+      <c r="U111" s="12" t="n">
+        <v>96891</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>103725</v>
+      </c>
+      <c r="W111" s="12" t="n">
+        <v>45216</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>-462</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>88</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>-123</v>
-      </c>
-      <c r="P112" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q112" s="22" t="n">
-        <v>-19</v>
-      </c>
-      <c r="R112" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="S112" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>-82</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>-140</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>-462</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>88</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>-123</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>지분법손익</t>
-        </is>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>-5371</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>-5309</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>-6460</v>
-      </c>
-      <c r="P113" s="22" t="n">
-        <v>-2071</v>
-      </c>
-      <c r="Q113" s="22" t="n">
-        <v>-548</v>
-      </c>
-      <c r="R113" s="22" t="n">
-        <v>-4158</v>
-      </c>
-      <c r="S113" s="22" t="n">
-        <v>-4528</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>-4983</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>-5624</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>-5371</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>-5309</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>-6460</v>
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 포괄이익</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>101516</v>
+      </c>
+      <c r="D112" s="12" t="n">
+        <v>77289</v>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>104809</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>103725</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>96743</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>112751</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>126489</v>
+      </c>
+      <c r="J112" s="12" t="n">
+        <v>45216</v>
+      </c>
+      <c r="K112" s="12" t="n">
+        <v>143967</v>
+      </c>
+      <c r="S112" s="12" t="n">
+        <v>-20685</v>
+      </c>
+      <c r="T112" s="12" t="n">
+        <v>25896</v>
+      </c>
+      <c r="U112" s="12" t="n">
+        <v>96891</v>
+      </c>
+      <c r="V112" s="12" t="n">
+        <v>103725</v>
+      </c>
+      <c r="W112" s="12" t="n">
+        <v>45216</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>매출채권 증감</t>
-        </is>
-      </c>
-      <c r="F114" s="22" t="n">
-        <v>4709</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>-18571</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>-36862</v>
-      </c>
-      <c r="P114" s="22" t="n">
-        <v>-31525</v>
-      </c>
-      <c r="Q114" s="22" t="n">
-        <v>-9569</v>
-      </c>
-      <c r="R114" s="22" t="n">
-        <v>4171</v>
-      </c>
-      <c r="S114" s="22" t="n">
-        <v>-21969</v>
-      </c>
-      <c r="T114" s="22" t="n">
-        <v>-53099</v>
-      </c>
-      <c r="U114" s="22" t="n">
-        <v>-36742</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>4709</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>-18571</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>-36862</v>
-      </c>
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B114" s="44" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="n"/>
+      <c r="D114" s="18" t="n"/>
+      <c r="E114" s="18" t="n"/>
+      <c r="F114" s="18" t="n"/>
+      <c r="G114" s="18" t="n"/>
+      <c r="H114" s="18" t="n"/>
+      <c r="I114" s="18" t="n"/>
+      <c r="J114" s="18" t="n"/>
+      <c r="K114" s="18" t="n"/>
+      <c r="L114" s="18" t="n"/>
+      <c r="M114" s="18" t="n"/>
+      <c r="N114" s="18" t="n"/>
+      <c r="O114" s="18" t="n"/>
+      <c r="P114" s="18" t="n"/>
+      <c r="Q114" s="18" t="n"/>
+      <c r="R114" s="18" t="n"/>
+      <c r="S114" s="18" t="n"/>
+      <c r="T114" s="18" t="n"/>
+      <c r="U114" s="18" t="n"/>
+      <c r="V114" s="18" t="n"/>
+      <c r="W114" s="18" t="n"/>
+      <c r="X114" s="18" t="n"/>
+      <c r="Y114" s="18" t="n"/>
+      <c r="Z114" s="18" t="n"/>
+      <c r="AA114" s="18" t="n"/>
+      <c r="AB114" s="18" t="n"/>
+      <c r="AC114" s="18" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>재고자산 증감</t>
-        </is>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>11280</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>-756</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>-5539</v>
-      </c>
-      <c r="P115" s="22" t="n">
-        <v>-10525</v>
-      </c>
-      <c r="Q115" s="22" t="n">
-        <v>-3482</v>
-      </c>
-      <c r="R115" s="22" t="n">
-        <v>4311</v>
-      </c>
-      <c r="S115" s="22" t="n">
-        <v>-943</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>-26257</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>-23961</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>11280</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>-756</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>-5539</v>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="H115" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="J115" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>2027.2Q</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
+          <t>2027.3Q</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>2027.4Q</t>
+        </is>
+      </c>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="R115" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="S115" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="T115" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="U115" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="V115" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W115" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="X115" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="Y115" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="Z115" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AA115" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AB115" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
+      </c>
+      <c r="AC115" s="5" t="inlineStr">
+        <is>
+          <t>2032(MW)</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>매입채무 증감</t>
-        </is>
-      </c>
-      <c r="F116" s="22" t="n">
-        <v>-4643</v>
-      </c>
-      <c r="J116" s="22" t="n">
-        <v>1160</v>
-      </c>
-      <c r="N116" s="22" t="n">
-        <v>-4396</v>
-      </c>
-      <c r="P116" s="22" t="n">
-        <v>3345</v>
-      </c>
-      <c r="Q116" s="22" t="n">
-        <v>-4355</v>
-      </c>
-      <c r="R116" s="22" t="n">
-        <v>3308</v>
-      </c>
-      <c r="S116" s="22" t="n">
-        <v>920</v>
-      </c>
-      <c r="T116" s="22" t="n">
-        <v>5334</v>
-      </c>
-      <c r="U116" s="22" t="n">
-        <v>2358</v>
-      </c>
-      <c r="V116" s="22" t="n">
-        <v>-4643</v>
-      </c>
-      <c r="W116" s="22" t="n">
-        <v>1160</v>
-      </c>
-      <c r="X116" s="22" t="n">
-        <v>-4396</v>
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>519295</v>
+      </c>
+      <c r="J116" s="12" t="n">
+        <v>561010</v>
+      </c>
+      <c r="N116" s="12" t="n">
+        <v>635756</v>
+      </c>
+      <c r="P116" s="12" t="n">
+        <v>298860</v>
+      </c>
+      <c r="Q116" s="12" t="n">
+        <v>319860</v>
+      </c>
+      <c r="R116" s="12" t="n">
+        <v>280253</v>
+      </c>
+      <c r="S116" s="12" t="n">
+        <v>286594</v>
+      </c>
+      <c r="T116" s="12" t="n">
+        <v>431240</v>
+      </c>
+      <c r="U116" s="12" t="n">
+        <v>512830</v>
+      </c>
+      <c r="V116" s="12" t="n">
+        <v>519295</v>
+      </c>
+      <c r="W116" s="12" t="n">
+        <v>561010</v>
+      </c>
+      <c r="X116" s="12" t="n">
+        <v>635756</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="F117" s="22" t="n">
-        <v>485</v>
+        <v>13767</v>
       </c>
       <c r="J117" s="22" t="n">
-        <v>1540</v>
+        <v>15193</v>
       </c>
       <c r="N117" s="22" t="n">
-        <v>3381</v>
+        <v>17227</v>
       </c>
       <c r="P117" s="22" t="n">
-        <v>1746</v>
+        <v>4577</v>
       </c>
       <c r="Q117" s="22" t="n">
-        <v>33</v>
+        <v>6288</v>
       </c>
       <c r="R117" s="22" t="n">
-        <v>23</v>
+        <v>7995</v>
       </c>
       <c r="S117" s="22" t="n">
-        <v>1184</v>
+        <v>7555</v>
       </c>
       <c r="T117" s="22" t="n">
-        <v>2773</v>
+        <v>8621</v>
       </c>
       <c r="U117" s="22" t="n">
-        <v>638</v>
+        <v>11523</v>
       </c>
       <c r="V117" s="22" t="n">
-        <v>485</v>
+        <v>13767</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>1540</v>
+        <v>15193</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>3381</v>
+        <v>17227</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="F118" s="22" t="n">
-        <v>4508</v>
+        <v>-5459</v>
       </c>
       <c r="J118" s="22" t="n">
-        <v>4478</v>
+        <v>-9083</v>
       </c>
       <c r="N118" s="22" t="n">
-        <v>13304</v>
+        <v>-16368</v>
       </c>
       <c r="P118" s="22" t="n">
-        <v>6</v>
+        <v>-988</v>
       </c>
       <c r="Q118" s="22" t="n">
-        <v>4013</v>
+        <v>-1245</v>
       </c>
       <c r="R118" s="22" t="n">
-        <v>-1261</v>
+        <v>-1326</v>
       </c>
       <c r="S118" s="22" t="n">
         <v>-838</v>
       </c>
       <c r="T118" s="22" t="n">
-        <v>3981</v>
+        <v>-646</v>
       </c>
       <c r="U118" s="22" t="n">
-        <v>-1730</v>
+        <v>-2129</v>
       </c>
       <c r="V118" s="22" t="n">
-        <v>4508</v>
+        <v>-5459</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>4478</v>
+        <v>-9083</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>13304</v>
+        <v>-16368</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="F119" s="22" t="n">
-        <v>538108</v>
+        <v>-462</v>
       </c>
       <c r="J119" s="22" t="n">
-        <v>549750</v>
+        <v>88</v>
       </c>
       <c r="N119" s="22" t="n">
-        <v>599918</v>
+        <v>-123</v>
       </c>
       <c r="P119" s="22" t="n">
-        <v>263447</v>
+        <v>20</v>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>310975</v>
+        <v>-19</v>
       </c>
       <c r="R119" s="22" t="n">
-        <v>293319</v>
+        <v>2</v>
       </c>
       <c r="S119" s="22" t="n">
-        <v>267134</v>
+        <v>-1</v>
       </c>
       <c r="T119" s="22" t="n">
-        <v>366881</v>
+        <v>-82</v>
       </c>
       <c r="U119" s="22" t="n">
-        <v>457021</v>
+        <v>-140</v>
       </c>
       <c r="V119" s="22" t="n">
-        <v>538108</v>
+        <v>-462</v>
       </c>
       <c r="W119" s="22" t="n">
-        <v>549750</v>
+        <v>88</v>
       </c>
       <c r="X119" s="22" t="n">
-        <v>599918</v>
+        <v>-123</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="F120" s="22" t="n">
-        <v>5606</v>
+        <v>-5371</v>
       </c>
       <c r="J120" s="22" t="n">
-        <v>8472</v>
+        <v>-5309</v>
       </c>
       <c r="N120" s="22" t="n">
-        <v>12406</v>
+        <v>-6460</v>
       </c>
       <c r="P120" s="22" t="n">
-        <v>1558</v>
+        <v>-2071</v>
       </c>
       <c r="Q120" s="22" t="n">
-        <v>1428</v>
+        <v>-548</v>
       </c>
       <c r="R120" s="22" t="n">
-        <v>1597</v>
+        <v>-4158</v>
       </c>
       <c r="S120" s="22" t="n">
-        <v>1158</v>
+        <v>-4528</v>
       </c>
       <c r="T120" s="22" t="n">
-        <v>1804</v>
+        <v>-4983</v>
       </c>
       <c r="U120" s="22" t="n">
-        <v>2490</v>
+        <v>-5624</v>
       </c>
       <c r="V120" s="22" t="n">
-        <v>5606</v>
+        <v>-5371</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>8472</v>
+        <v>-5309</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>12406</v>
+        <v>-6460</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="F121" s="22" t="n">
-        <v>-155798</v>
+        <v>4709</v>
       </c>
       <c r="J121" s="22" t="n">
-        <v>-148699</v>
+        <v>-18571</v>
       </c>
       <c r="N121" s="22" t="n">
-        <v>-181644</v>
+        <v>-36862</v>
       </c>
       <c r="P121" s="22" t="n">
-        <v>-62071</v>
+        <v>-31525</v>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>-103024</v>
+        <v>-9569</v>
       </c>
       <c r="R121" s="22" t="n">
-        <v>-91481</v>
+        <v>4171</v>
       </c>
       <c r="S121" s="22" t="n">
-        <v>-75640</v>
+        <v>-21969</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>-97210</v>
+        <v>-53099</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>-156884</v>
+        <v>-36742</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>-155798</v>
+        <v>4709</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>-148699</v>
+        <v>-18571</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>-181644</v>
+        <v>-36862</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="n">
-        <v>387916</v>
-      </c>
-      <c r="J122" s="12" t="n">
-        <v>409522</v>
-      </c>
-      <c r="N122" s="12" t="n">
-        <v>430680</v>
-      </c>
-      <c r="P122" s="12" t="n">
-        <v>202934</v>
-      </c>
-      <c r="Q122" s="12" t="n">
-        <v>209380</v>
-      </c>
-      <c r="R122" s="12" t="n">
-        <v>203434</v>
-      </c>
-      <c r="S122" s="12" t="n">
-        <v>192652</v>
-      </c>
-      <c r="T122" s="12" t="n">
-        <v>271476</v>
-      </c>
-      <c r="U122" s="12" t="n">
-        <v>302628</v>
-      </c>
-      <c r="V122" s="12" t="n">
-        <v>387916</v>
-      </c>
-      <c r="W122" s="12" t="n">
-        <v>409522</v>
-      </c>
-      <c r="X122" s="12" t="n">
-        <v>430680</v>
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>11280</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>-756</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>-5539</v>
+      </c>
+      <c r="P122" s="22" t="n">
+        <v>-10525</v>
+      </c>
+      <c r="Q122" s="22" t="n">
+        <v>-3482</v>
+      </c>
+      <c r="R122" s="22" t="n">
+        <v>4311</v>
+      </c>
+      <c r="S122" s="22" t="n">
+        <v>-943</v>
+      </c>
+      <c r="T122" s="22" t="n">
+        <v>-26257</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>-23961</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>11280</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>-756</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>-5539</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>정기예금 증감</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="F123" s="22" t="n">
-        <v>-16099</v>
+        <v>-4643</v>
       </c>
       <c r="J123" s="22" t="n">
-        <v>-14758</v>
+        <v>1160</v>
       </c>
       <c r="N123" s="22" t="n">
-        <v>-8776</v>
+        <v>-4396</v>
       </c>
       <c r="P123" s="22" t="n">
-        <v>-115007</v>
+        <v>3345</v>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>-45644</v>
+        <v>-4355</v>
       </c>
       <c r="R123" s="22" t="n">
-        <v>-53413</v>
+        <v>3308</v>
       </c>
       <c r="S123" s="22" t="n">
-        <v>45365</v>
+        <v>920</v>
       </c>
       <c r="T123" s="22" t="n">
-        <v>132567</v>
+        <v>5334</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>-12659</v>
+        <v>2358</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>-16099</v>
+        <v>-4643</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>-14758</v>
+        <v>1160</v>
       </c>
       <c r="X123" s="22" t="n">
-        <v>-8776</v>
+        <v>-4396</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Short Term Investment Securities Inv CF</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="F124" s="22" t="n">
-        <v>-211264</v>
+        <v>485</v>
       </c>
       <c r="J124" s="22" t="n">
-        <v>-248539</v>
+        <v>1540</v>
       </c>
       <c r="N124" s="22" t="n">
-        <v>-243114</v>
+        <v>3381</v>
       </c>
       <c r="P124" s="22" t="n">
-        <v>-155502</v>
+        <v>1746</v>
       </c>
       <c r="Q124" s="22" t="n">
-        <v>-150006</v>
+        <v>33</v>
       </c>
       <c r="R124" s="22" t="n">
-        <v>-159990</v>
+        <v>23</v>
       </c>
       <c r="S124" s="22" t="n">
-        <v>-217793</v>
+        <v>1184</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>-136490</v>
+        <v>2773</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>-229974</v>
+        <v>638</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>-211264</v>
+        <v>485</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>-248539</v>
+        <v>1540</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>-243114</v>
+        <v>3381</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="F125" s="22" t="n">
-        <v>-12492</v>
+        <v>4508</v>
       </c>
       <c r="J125" s="22" t="n">
-        <v>-14342</v>
+        <v>4478</v>
       </c>
       <c r="N125" s="22" t="n">
-        <v>-28371</v>
+        <v>13304</v>
       </c>
       <c r="P125" s="22" t="n">
-        <v>-6770</v>
+        <v>6</v>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>-7361</v>
+        <v>4013</v>
       </c>
       <c r="R125" s="22" t="n">
-        <v>-8243</v>
+        <v>-1261</v>
       </c>
       <c r="S125" s="22" t="n">
-        <v>-4358</v>
+        <v>-838</v>
       </c>
       <c r="T125" s="22" t="n">
-        <v>-6162</v>
+        <v>3981</v>
       </c>
       <c r="U125" s="22" t="n">
-        <v>-39345</v>
+        <v>-1730</v>
       </c>
       <c r="V125" s="22" t="n">
-        <v>-12492</v>
+        <v>4508</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>-14342</v>
+        <v>4478</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>-28371</v>
+        <v>13304</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="F126" s="22" t="n">
-        <v>-2935</v>
+        <v>538108</v>
       </c>
       <c r="J126" s="22" t="n">
-        <v>-2971</v>
+        <v>549750</v>
       </c>
       <c r="N126" s="22" t="n">
-        <v>-32124</v>
+        <v>599918</v>
       </c>
       <c r="P126" s="22" t="n">
-        <v>-2928</v>
+        <v>263447</v>
       </c>
       <c r="Q126" s="22" t="n">
-        <v>-2337</v>
+        <v>310975</v>
       </c>
       <c r="R126" s="22" t="n">
-        <v>-1064</v>
+        <v>293319</v>
       </c>
       <c r="S126" s="22" t="n">
-        <v>-700</v>
+        <v>267134</v>
       </c>
       <c r="T126" s="22" t="n">
-        <v>-1049</v>
+        <v>366881</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>-1507</v>
+        <v>457021</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>-2935</v>
+        <v>538108</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>-2971</v>
+        <v>549750</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>-32124</v>
+        <v>599918</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="F127" s="12" t="n">
-        <v>-242792</v>
-      </c>
-      <c r="J127" s="12" t="n">
-        <v>-280612</v>
-      </c>
-      <c r="N127" s="12" t="n">
-        <v>-312387</v>
-      </c>
-      <c r="P127" s="12" t="n">
-        <v>-280208</v>
-      </c>
-      <c r="Q127" s="12" t="n">
-        <v>-205350</v>
-      </c>
-      <c r="R127" s="12" t="n">
-        <v>-222712</v>
-      </c>
-      <c r="S127" s="12" t="n">
-        <v>-177487</v>
-      </c>
-      <c r="T127" s="12" t="n">
-        <v>-11134</v>
-      </c>
-      <c r="U127" s="12" t="n">
-        <v>-283487</v>
-      </c>
-      <c r="V127" s="12" t="n">
-        <v>-242792</v>
-      </c>
-      <c r="W127" s="12" t="n">
-        <v>-280612</v>
-      </c>
-      <c r="X127" s="12" t="n">
-        <v>-312387</v>
+      <c r="A127" s="20" t="inlineStr">
+        <is>
+          <t>이자·배당금 수취</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>5606</v>
+      </c>
+      <c r="J127" s="22" t="n">
+        <v>8472</v>
+      </c>
+      <c r="N127" s="22" t="n">
+        <v>12406</v>
+      </c>
+      <c r="P127" s="22" t="n">
+        <v>1558</v>
+      </c>
+      <c r="Q127" s="22" t="n">
+        <v>1428</v>
+      </c>
+      <c r="R127" s="22" t="n">
+        <v>1597</v>
+      </c>
+      <c r="S127" s="22" t="n">
+        <v>1158</v>
+      </c>
+      <c r="T127" s="22" t="n">
+        <v>1804</v>
+      </c>
+      <c r="U127" s="22" t="n">
+        <v>2490</v>
+      </c>
+      <c r="V127" s="22" t="n">
+        <v>5606</v>
+      </c>
+      <c r="W127" s="22" t="n">
+        <v>8472</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>12406</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>자기주식 증감액</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="F128" s="22" t="n">
-        <v>-23</v>
+        <v>-155798</v>
       </c>
       <c r="J128" s="22" t="n">
-        <v>-19</v>
+        <v>-148699</v>
       </c>
       <c r="N128" s="22" t="n">
-        <v>-12</v>
+        <v>-181644</v>
       </c>
       <c r="P128" s="22" t="n">
-        <v>-45</v>
+        <v>-62071</v>
       </c>
       <c r="Q128" s="22" t="n">
-        <v>-31</v>
+        <v>-103024</v>
       </c>
       <c r="R128" s="22" t="n">
-        <v>-43</v>
+        <v>-91481</v>
       </c>
       <c r="S128" s="22" t="n">
-        <v>-26</v>
+        <v>-75640</v>
       </c>
       <c r="T128" s="22" t="n">
-        <v>-22</v>
+        <v>-97210</v>
       </c>
       <c r="U128" s="22" t="n">
-        <v>-10</v>
+        <v>-156884</v>
       </c>
       <c r="V128" s="22" t="n">
-        <v>-23</v>
+        <v>-155798</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>-19</v>
+        <v>-148699</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>-12</v>
+        <v>-181644</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="F129" s="22" t="n">
-        <v>-72757</v>
-      </c>
-      <c r="J129" s="22" t="n">
-        <v>-78820</v>
-      </c>
-      <c r="N129" s="22" t="n">
-        <v>-109136</v>
-      </c>
-      <c r="P129" s="22" t="n">
-        <v>-15158</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>-18189</v>
-      </c>
-      <c r="R129" s="22" t="n">
-        <v>-24252</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>-48505</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-48505</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>-60631</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>-72757</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>-78820</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>-109136</v>
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>387916</v>
+      </c>
+      <c r="J129" s="12" t="n">
+        <v>409522</v>
+      </c>
+      <c r="N129" s="12" t="n">
+        <v>430680</v>
+      </c>
+      <c r="P129" s="12" t="n">
+        <v>202934</v>
+      </c>
+      <c r="Q129" s="12" t="n">
+        <v>209380</v>
+      </c>
+      <c r="R129" s="12" t="n">
+        <v>203434</v>
+      </c>
+      <c r="S129" s="12" t="n">
+        <v>192652</v>
+      </c>
+      <c r="T129" s="12" t="n">
+        <v>271476</v>
+      </c>
+      <c r="U129" s="12" t="n">
+        <v>302628</v>
+      </c>
+      <c r="V129" s="12" t="n">
+        <v>387916</v>
+      </c>
+      <c r="W129" s="12" t="n">
+        <v>409522</v>
+      </c>
+      <c r="X129" s="12" t="n">
+        <v>430680</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>정기예금 증감</t>
         </is>
       </c>
       <c r="F130" s="22" t="n">
-        <v>-3525</v>
+        <v>-16099</v>
       </c>
       <c r="J130" s="22" t="n">
-        <v>-4589</v>
+        <v>-14758</v>
       </c>
       <c r="N130" s="22" t="n">
-        <v>-4573</v>
+        <v>-8776</v>
+      </c>
+      <c r="P130" s="22" t="n">
+        <v>-115007</v>
+      </c>
+      <c r="Q130" s="22" t="n">
+        <v>-45644</v>
+      </c>
+      <c r="R130" s="22" t="n">
+        <v>-53413</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>0</v>
+        <v>45365</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-1290</v>
+        <v>132567</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-3024</v>
+        <v>-12659</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-3525</v>
+        <v>-16099</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-4589</v>
+        <v>-14758</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-4573</v>
+        <v>-8776</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="F131" s="12" t="n">
-        <v>-76306</v>
-      </c>
-      <c r="J131" s="12" t="n">
-        <v>-83430</v>
-      </c>
-      <c r="N131" s="12" t="n">
-        <v>-113722</v>
-      </c>
-      <c r="P131" s="12" t="n">
-        <v>-15203</v>
-      </c>
-      <c r="Q131" s="12" t="n">
-        <v>-18221</v>
-      </c>
-      <c r="R131" s="12" t="n">
-        <v>-24296</v>
-      </c>
-      <c r="S131" s="12" t="n">
-        <v>-48532</v>
-      </c>
-      <c r="T131" s="12" t="n">
-        <v>-49817</v>
-      </c>
-      <c r="U131" s="12" t="n">
-        <v>-63666</v>
-      </c>
-      <c r="V131" s="12" t="n">
-        <v>-76306</v>
-      </c>
-      <c r="W131" s="12" t="n">
-        <v>-83430</v>
-      </c>
-      <c r="X131" s="12" t="n">
-        <v>-113722</v>
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>Decrease Increase In Short Term Investment Securities Inv CF</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>-211264</v>
+      </c>
+      <c r="J131" s="22" t="n">
+        <v>-248539</v>
+      </c>
+      <c r="N131" s="22" t="n">
+        <v>-243114</v>
+      </c>
+      <c r="P131" s="22" t="n">
+        <v>-155502</v>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>-150006</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>-159990</v>
+      </c>
+      <c r="S131" s="22" t="n">
+        <v>-217793</v>
+      </c>
+      <c r="T131" s="22" t="n">
+        <v>-136490</v>
+      </c>
+      <c r="U131" s="22" t="n">
+        <v>-229974</v>
+      </c>
+      <c r="V131" s="22" t="n">
+        <v>-211264</v>
+      </c>
+      <c r="W131" s="22" t="n">
+        <v>-248539</v>
+      </c>
+      <c r="X131" s="22" t="n">
+        <v>-243114</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-6754</v>
+        <v>-12492</v>
       </c>
       <c r="J132" s="22" t="n">
-        <v>169</v>
+        <v>-14342</v>
       </c>
       <c r="N132" s="22" t="n">
-        <v>-5016</v>
+        <v>-28371</v>
       </c>
       <c r="P132" s="22" t="n">
-        <v>123</v>
+        <v>-6770</v>
       </c>
       <c r="Q132" s="22" t="n">
-        <v>-174</v>
+        <v>-7361</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>582</v>
+        <v>-8243</v>
       </c>
       <c r="S132" s="22" t="n">
-        <v>338</v>
+        <v>-4358</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>-4233</v>
+        <v>-6162</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-7636</v>
+        <v>-39345</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-6754</v>
+        <v>-12492</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>169</v>
+        <v>-14342</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>-5016</v>
+        <v>-28371</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>-2935</v>
+      </c>
+      <c r="J133" s="22" t="n">
+        <v>-2971</v>
+      </c>
+      <c r="N133" s="22" t="n">
+        <v>-32124</v>
+      </c>
+      <c r="P133" s="22" t="n">
+        <v>-2928</v>
+      </c>
+      <c r="Q133" s="22" t="n">
+        <v>-2337</v>
+      </c>
+      <c r="R133" s="22" t="n">
+        <v>-1064</v>
+      </c>
+      <c r="S133" s="22" t="n">
+        <v>-700</v>
+      </c>
+      <c r="T133" s="22" t="n">
+        <v>-1049</v>
+      </c>
+      <c r="U133" s="22" t="n">
+        <v>-1507</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>-2935</v>
+      </c>
+      <c r="W133" s="22" t="n">
+        <v>-2971</v>
+      </c>
+      <c r="X133" s="22" t="n">
+        <v>-32124</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>-242792</v>
+      </c>
+      <c r="J134" s="12" t="n">
+        <v>-280612</v>
+      </c>
+      <c r="N134" s="12" t="n">
+        <v>-312387</v>
+      </c>
+      <c r="P134" s="12" t="n">
+        <v>-280208</v>
+      </c>
+      <c r="Q134" s="12" t="n">
+        <v>-205350</v>
+      </c>
+      <c r="R134" s="12" t="n">
+        <v>-222712</v>
+      </c>
+      <c r="S134" s="12" t="n">
+        <v>-177487</v>
+      </c>
+      <c r="T134" s="12" t="n">
+        <v>-11134</v>
+      </c>
+      <c r="U134" s="12" t="n">
+        <v>-283487</v>
+      </c>
+      <c r="V134" s="12" t="n">
+        <v>-242792</v>
+      </c>
+      <c r="W134" s="12" t="n">
+        <v>-280612</v>
+      </c>
+      <c r="X134" s="12" t="n">
+        <v>-312387</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 증감액</t>
+        </is>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>-23</v>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>-12</v>
+      </c>
+      <c r="P135" s="22" t="n">
+        <v>-45</v>
+      </c>
+      <c r="Q135" s="22" t="n">
+        <v>-31</v>
+      </c>
+      <c r="R135" s="22" t="n">
+        <v>-43</v>
+      </c>
+      <c r="S135" s="22" t="n">
+        <v>-26</v>
+      </c>
+      <c r="T135" s="22" t="n">
+        <v>-22</v>
+      </c>
+      <c r="U135" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="V135" s="22" t="n">
+        <v>-23</v>
+      </c>
+      <c r="W135" s="22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="X135" s="22" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="F136" s="22" t="n">
+        <v>-72757</v>
+      </c>
+      <c r="J136" s="22" t="n">
+        <v>-78820</v>
+      </c>
+      <c r="N136" s="22" t="n">
+        <v>-109136</v>
+      </c>
+      <c r="P136" s="22" t="n">
+        <v>-15158</v>
+      </c>
+      <c r="Q136" s="22" t="n">
+        <v>-18189</v>
+      </c>
+      <c r="R136" s="22" t="n">
+        <v>-24252</v>
+      </c>
+      <c r="S136" s="22" t="n">
+        <v>-48505</v>
+      </c>
+      <c r="T136" s="22" t="n">
+        <v>-48505</v>
+      </c>
+      <c r="U136" s="22" t="n">
+        <v>-60631</v>
+      </c>
+      <c r="V136" s="22" t="n">
+        <v>-72757</v>
+      </c>
+      <c r="W136" s="22" t="n">
+        <v>-78820</v>
+      </c>
+      <c r="X136" s="22" t="n">
+        <v>-109136</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>-3525</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-4589</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>-4573</v>
+      </c>
+      <c r="S137" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="22" t="n">
+        <v>-1290</v>
+      </c>
+      <c r="U137" s="22" t="n">
+        <v>-3024</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>-3525</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-4589</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-4573</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>-76306</v>
+      </c>
+      <c r="J138" s="12" t="n">
+        <v>-83430</v>
+      </c>
+      <c r="N138" s="12" t="n">
+        <v>-113722</v>
+      </c>
+      <c r="P138" s="12" t="n">
+        <v>-15203</v>
+      </c>
+      <c r="Q138" s="12" t="n">
+        <v>-18221</v>
+      </c>
+      <c r="R138" s="12" t="n">
+        <v>-24296</v>
+      </c>
+      <c r="S138" s="12" t="n">
+        <v>-48532</v>
+      </c>
+      <c r="T138" s="12" t="n">
+        <v>-49817</v>
+      </c>
+      <c r="U138" s="12" t="n">
+        <v>-63666</v>
+      </c>
+      <c r="V138" s="12" t="n">
+        <v>-76306</v>
+      </c>
+      <c r="W138" s="12" t="n">
+        <v>-83430</v>
+      </c>
+      <c r="X138" s="12" t="n">
+        <v>-113722</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="F139" s="22" t="n">
+        <v>-6754</v>
+      </c>
+      <c r="J139" s="22" t="n">
+        <v>169</v>
+      </c>
+      <c r="N139" s="22" t="n">
+        <v>-5016</v>
+      </c>
+      <c r="P139" s="22" t="n">
+        <v>123</v>
+      </c>
+      <c r="Q139" s="22" t="n">
+        <v>-174</v>
+      </c>
+      <c r="R139" s="22" t="n">
+        <v>582</v>
+      </c>
+      <c r="S139" s="22" t="n">
+        <v>338</v>
+      </c>
+      <c r="T139" s="22" t="n">
+        <v>-4233</v>
+      </c>
+      <c r="U139" s="22" t="n">
+        <v>-7636</v>
+      </c>
+      <c r="V139" s="22" t="n">
+        <v>-6754</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>169</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>-5016</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="F133" s="22" t="n">
+      <c r="F140" s="22" t="n">
         <v>62062</v>
       </c>
-      <c r="J133" s="22" t="n">
+      <c r="J140" s="22" t="n">
         <v>45649</v>
       </c>
-      <c r="N133" s="22" t="n">
+      <c r="N140" s="22" t="n">
         <v>-445</v>
       </c>
-      <c r="P133" s="22" t="n">
+      <c r="P140" s="22" t="n">
         <v>-92354</v>
       </c>
-      <c r="Q133" s="22" t="n">
+      <c r="Q140" s="22" t="n">
         <v>-14366</v>
       </c>
-      <c r="R133" s="22" t="n">
+      <c r="R140" s="22" t="n">
         <v>-42990</v>
       </c>
-      <c r="S133" s="22" t="n">
+      <c r="S140" s="22" t="n">
         <v>-33028</v>
       </c>
-      <c r="T133" s="22" t="n">
+      <c r="T140" s="22" t="n">
         <v>206290</v>
       </c>
-      <c r="U133" s="22" t="n">
+      <c r="U140" s="22" t="n">
         <v>-52162</v>
       </c>
-      <c r="V133" s="22" t="n">
+      <c r="V140" s="22" t="n">
         <v>62062</v>
       </c>
-      <c r="W133" s="22" t="n">
+      <c r="W140" s="22" t="n">
         <v>45649</v>
       </c>
-      <c r="X133" s="22" t="n">
+      <c r="X140" s="22" t="n">
         <v>-445</v>
       </c>
     </row>
@@ -8278,7 +8665,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -9674,7 +10061,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -9726,7 +10113,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -9778,7 +10165,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -9830,7 +10217,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -9882,7 +10269,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -9934,7 +10321,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -9986,7 +10373,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -9996,43 +10383,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!E44:H44)&lt;4,"",SUM('연간'!E44:H44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!F44:I44)&lt;4,"",SUM('연간'!F44:I44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!O44)&lt;=0,"적자",H28/('연간'!O44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",I28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",J28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",K28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",L28/('연간'!W44)),"")</f>
         <v/>
       </c>
@@ -10056,7 +10443,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10108,7 +10495,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10160,7 +10547,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10212,7 +10599,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10264,7 +10651,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10316,7 +10703,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10386,7 +10773,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -10438,7 +10825,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -10448,49 +10835,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!O4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -10500,49 +10887,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!O11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -10552,49 +10939,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!O11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -10604,43 +10991,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -10664,7 +11051,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -10716,7 +11103,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -10768,7 +11155,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -10820,7 +11207,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -12492,24 +12879,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>

--- a/docs/data/jp/xlsx/6861.xlsx
+++ b/docs/data/jp/xlsx/6861.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터 데이터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'연간'!$3:$3</definedName>
@@ -21,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;;-0.0&quot;x&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;년&quot;;-0.0&quot;년&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;;-0&quot;일&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,11 +128,31 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -155,6 +177,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -201,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -345,7 +372,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -757,7 +799,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6861 Model</t>
+          <t>키엔스 Model</t>
         </is>
       </c>
     </row>
@@ -968,7 +1010,9 @@
       <c r="K4" s="12" t="n">
         <v>346621</v>
       </c>
-      <c r="L4" s="12" t="n"/>
+      <c r="L4" s="12" t="n">
+        <v>388778</v>
+      </c>
       <c r="M4" s="12" t="n"/>
       <c r="N4" s="12" t="n"/>
       <c r="O4" s="11" t="n"/>
@@ -1481,7 +1525,9 @@
       <c r="K11" s="22" t="n">
         <v>51866</v>
       </c>
-      <c r="L11" s="22" t="n"/>
+      <c r="L11" s="22" t="n">
+        <v>53567</v>
+      </c>
       <c r="M11" s="22" t="n"/>
       <c r="N11" s="22" t="n"/>
       <c r="O11" s="21" t="n"/>
@@ -2006,7 +2052,9 @@
       <c r="K17" s="22" t="n">
         <v>107679</v>
       </c>
-      <c r="L17" s="22" t="n"/>
+      <c r="L17" s="22" t="n">
+        <v>114024</v>
+      </c>
       <c r="M17" s="22" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="21" t="n"/>
@@ -2182,7 +2230,9 @@
       <c r="K19" s="12" t="n">
         <v>187076</v>
       </c>
-      <c r="L19" s="12" t="n"/>
+      <c r="L19" s="12" t="n">
+        <v>221186</v>
+      </c>
       <c r="M19" s="12" t="n"/>
       <c r="N19" s="12" t="n"/>
       <c r="O19" s="11" t="n"/>
@@ -3499,7 +3549,9 @@
       <c r="K39" s="22" t="n">
         <v>9798</v>
       </c>
-      <c r="L39" s="22" t="n"/>
+      <c r="L39" s="22" t="n">
+        <v>9001</v>
+      </c>
       <c r="M39" s="22" t="n"/>
       <c r="N39" s="22" t="n"/>
       <c r="O39" s="21" t="n"/>
@@ -3701,7 +3753,9 @@
       <c r="K41" s="22" t="n">
         <v>81</v>
       </c>
-      <c r="L41" s="22" t="n"/>
+      <c r="L41" s="22" t="n">
+        <v>2632</v>
+      </c>
       <c r="M41" s="22" t="n"/>
       <c r="N41" s="22" t="n"/>
       <c r="O41" s="21" t="n"/>
@@ -3903,7 +3957,9 @@
       <c r="K43" s="12" t="n">
         <v>196793</v>
       </c>
-      <c r="L43" s="12" t="n"/>
+      <c r="L43" s="12" t="n">
+        <v>227555</v>
+      </c>
       <c r="M43" s="12" t="n"/>
       <c r="N43" s="12" t="n"/>
       <c r="O43" s="11" t="n"/>
@@ -4090,7 +4146,9 @@
       <c r="K45" s="22" t="n">
         <v>57660</v>
       </c>
-      <c r="L45" s="22" t="n"/>
+      <c r="L45" s="22" t="n">
+        <v>68012</v>
+      </c>
       <c r="M45" s="22" t="n"/>
       <c r="N45" s="22" t="n"/>
       <c r="O45" s="21" t="n"/>
@@ -4291,7 +4349,9 @@
       <c r="K47" s="12" t="n">
         <v>139133</v>
       </c>
-      <c r="L47" s="12" t="n"/>
+      <c r="L47" s="12" t="n">
+        <v>159542</v>
+      </c>
       <c r="M47" s="12" t="n"/>
       <c r="N47" s="12" t="n"/>
       <c r="O47" s="11" t="n"/>
@@ -4478,7 +4538,9 @@
       <c r="K49" s="12" t="n">
         <v>139133</v>
       </c>
-      <c r="L49" s="12" t="n"/>
+      <c r="L49" s="12" t="n">
+        <v>159542</v>
+      </c>
       <c r="M49" s="12" t="n"/>
       <c r="N49" s="12" t="n"/>
       <c r="O49" s="11" t="n"/>
@@ -4784,11 +4846,11 @@
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.28)</t>
+          <t>현재 주가 (2026.10.29)</t>
         </is>
       </c>
       <c r="B53" s="29" t="n">
-        <v>79510</v>
+        <v>76360</v>
       </c>
       <c r="C53" s="30" t="n"/>
       <c r="D53" s="31" t="n"/>
@@ -6025,7 +6087,7 @@
     <row r="80">
       <c r="A80" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.28</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.29</t>
         </is>
       </c>
       <c r="C80" s="41" t="n"/>
@@ -6251,6 +6313,9 @@
       <c r="K84" s="12" t="n">
         <v>346621</v>
       </c>
+      <c r="L84" s="12" t="n">
+        <v>388778</v>
+      </c>
       <c r="S84" s="12" t="n">
         <v>-7198</v>
       </c>
@@ -6298,6 +6363,10 @@
         <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
         <v/>
       </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
       <c r="S85" s="17">
         <f>IF(OR(S84="",R84=""),"",IF(R84&lt;=0,"",IFERROR(S84/R84-1,"")))</f>
         <v/>
@@ -6352,6 +6421,9 @@
       <c r="K86" s="22" t="n">
         <v>51866</v>
       </c>
+      <c r="L86" s="22" t="n">
+        <v>53567</v>
+      </c>
       <c r="S86" s="22" t="n">
         <v>2048</v>
       </c>
@@ -6399,6 +6471,10 @@
         <f>IF(OR(K86="",G86=""),"",IF(K86*G86&lt;=0,"",IFERROR(K86/G86-1,"")))</f>
         <v/>
       </c>
+      <c r="L87" s="17">
+        <f>IF(OR(L86="",H86=""),"",IF(L86*H86&lt;=0,"",IFERROR(L86/H86-1,"")))</f>
+        <v/>
+      </c>
       <c r="S87" s="17">
         <f>IF(OR(S86="",R86=""),"",IF(S86*R86&lt;=0,"",IFERROR(S86/R86-1,"")))</f>
         <v/>
@@ -6453,6 +6529,9 @@
       <c r="K88" s="12" t="n">
         <v>294755</v>
       </c>
+      <c r="L88" s="12" t="n">
+        <v>335211</v>
+      </c>
       <c r="S88" s="12" t="n">
         <v>-9246</v>
       </c>
@@ -6500,6 +6579,10 @@
         <f>IF(OR(K88="",G88=""),"",IF(G88&lt;=0,"",IFERROR(K88/G88-1,"")))</f>
         <v/>
       </c>
+      <c r="L89" s="17">
+        <f>IF(OR(L88="",H88=""),"",IF(H88&lt;=0,"",IFERROR(L88/H88-1,"")))</f>
+        <v/>
+      </c>
       <c r="S89" s="17">
         <f>IF(OR(S88="",R88=""),"",IF(R88&lt;=0,"",IFERROR(S88/R88-1,"")))</f>
         <v/>
@@ -6554,6 +6637,9 @@
       <c r="K90" s="22" t="n">
         <v>107679</v>
       </c>
+      <c r="L90" s="22" t="n">
+        <v>114024</v>
+      </c>
       <c r="S90" s="22" t="n">
         <v>16406</v>
       </c>
@@ -6601,6 +6687,10 @@
         <f>IF(OR(K90="",G90=""),"",IF(K90*G90&lt;=0,"",IFERROR(K90/G90-1,"")))</f>
         <v/>
       </c>
+      <c r="L91" s="17">
+        <f>IF(OR(L90="",H90=""),"",IF(L90*H90&lt;=0,"",IFERROR(L90/H90-1,"")))</f>
+        <v/>
+      </c>
       <c r="S91" s="17">
         <f>IF(OR(S90="",R90=""),"",IF(S90*R90&lt;=0,"",IFERROR(S90/R90-1,"")))</f>
         <v/>
@@ -6655,6 +6745,9 @@
       <c r="K92" s="12" t="n">
         <v>187076</v>
       </c>
+      <c r="L92" s="12" t="n">
+        <v>221186</v>
+      </c>
       <c r="S92" s="12" t="n">
         <v>-25653</v>
       </c>
@@ -6718,6 +6811,10 @@
         <f>IF(OR(K92="",K84=""),"",IF(K84&lt;=0,"",IFERROR(K92/K84,"")))</f>
         <v/>
       </c>
+      <c r="L93" s="17">
+        <f>IF(OR(L92="",L84=""),"",IF(L84&lt;=0,"",IFERROR(L92/L84,"")))</f>
+        <v/>
+      </c>
       <c r="S93" s="17">
         <f>IF(OR(S92="",S84=""),"",IF(S84&lt;=0,"",IFERROR(S92/S84,"")))</f>
         <v/>
@@ -6770,6 +6867,10 @@
         <f>IF(OR(K92="",G92=""),"",IF(G92&lt;=0,"",IFERROR(K92/G92-1,"")))</f>
         <v/>
       </c>
+      <c r="L94" s="17">
+        <f>IF(OR(L92="",H92=""),"",IF(H92&lt;=0,"",IFERROR(L92/H92-1,"")))</f>
+        <v/>
+      </c>
       <c r="S94" s="17">
         <f>IF(OR(S92="",R92=""),"",IF(R92&lt;=0,"",IFERROR(S92/R92-1,"")))</f>
         <v/>
@@ -6824,6 +6925,9 @@
       <c r="K95" s="22" t="n">
         <v>6091</v>
       </c>
+      <c r="L95" s="22" t="n">
+        <v>7876</v>
+      </c>
       <c r="S95" s="22" t="n">
         <v>342</v>
       </c>
@@ -6873,6 +6977,9 @@
       <c r="K96" s="22" t="n">
         <v>1295</v>
       </c>
+      <c r="L96" s="22" t="n">
+        <v>1907</v>
+      </c>
       <c r="S96" s="22" t="n">
         <v>794</v>
       </c>
@@ -6922,6 +7029,9 @@
       <c r="K97" s="22" t="n">
         <v>2243</v>
       </c>
+      <c r="L97" s="22" t="n">
+        <v>-2243</v>
+      </c>
       <c r="S97" s="22" t="n">
         <v>1173</v>
       </c>
@@ -6971,6 +7081,9 @@
       <c r="K98" s="22" t="n">
         <v>168</v>
       </c>
+      <c r="L98" s="22" t="n">
+        <v>1461</v>
+      </c>
       <c r="S98" s="22" t="n">
         <v>81</v>
       </c>
@@ -7020,6 +7133,9 @@
       <c r="K99" s="22" t="n">
         <v>9798</v>
       </c>
+      <c r="L99" s="22" t="n">
+        <v>9001</v>
+      </c>
       <c r="S99" s="22" t="n">
         <v>2391</v>
       </c>
@@ -7067,6 +7183,10 @@
         <f>IF(OR(K99="",G99=""),"",IF(K99*G99&lt;=0,"",IFERROR(K99/G99-1,"")))</f>
         <v/>
       </c>
+      <c r="L100" s="17">
+        <f>IF(OR(L99="",H99=""),"",IF(L99*H99&lt;=0,"",IFERROR(L99/H99-1,"")))</f>
+        <v/>
+      </c>
       <c r="S100" s="17">
         <f>IF(OR(S99="",R99=""),"",IF(S99*R99&lt;=0,"",IFERROR(S99/R99-1,"")))</f>
         <v/>
@@ -7109,6 +7229,9 @@
       <c r="K101" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="L101" s="22" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
@@ -7143,6 +7266,9 @@
       <c r="K102" s="22" t="n">
         <v>81</v>
       </c>
+      <c r="L102" s="22" t="n">
+        <v>640</v>
+      </c>
       <c r="S102" s="22" t="n">
         <v>-8</v>
       </c>
@@ -7192,6 +7318,9 @@
       <c r="K103" s="22" t="n">
         <v>81</v>
       </c>
+      <c r="L103" s="22" t="n">
+        <v>2632</v>
+      </c>
       <c r="S103" s="22" t="n">
         <v>-8</v>
       </c>
@@ -7239,6 +7368,10 @@
         <f>IF(OR(K103="",G103=""),"",IF(K103*G103&lt;=0,"",IFERROR(K103/G103-1,"")))</f>
         <v/>
       </c>
+      <c r="L104" s="17">
+        <f>IF(OR(L103="",H103=""),"",IF(L103*H103&lt;=0,"",IFERROR(L103/H103-1,"")))</f>
+        <v/>
+      </c>
       <c r="S104" s="17">
         <f>IF(OR(S103="",R103=""),"",IF(S103*R103&lt;=0,"",IFERROR(S103/R103-1,"")))</f>
         <v/>
@@ -7293,6 +7426,9 @@
       <c r="K105" s="12" t="n">
         <v>196793</v>
       </c>
+      <c r="L105" s="12" t="n">
+        <v>227555</v>
+      </c>
       <c r="S105" s="12" t="n">
         <v>-23254</v>
       </c>
@@ -7340,6 +7476,10 @@
         <f>IF(OR(K105="",G105=""),"",IF(G105&lt;=0,"",IFERROR(K105/G105-1,"")))</f>
         <v/>
       </c>
+      <c r="L106" s="17">
+        <f>IF(OR(L105="",H105=""),"",IF(H105&lt;=0,"",IFERROR(L105/H105-1,"")))</f>
+        <v/>
+      </c>
       <c r="S106" s="17">
         <f>IF(OR(S105="",R105=""),"",IF(R105&lt;=0,"",IFERROR(S105/R105-1,"")))</f>
         <v/>
@@ -7394,6 +7534,9 @@
       <c r="K107" s="12" t="n">
         <v>196793</v>
       </c>
+      <c r="L107" s="12" t="n">
+        <v>227555</v>
+      </c>
       <c r="S107" s="12" t="n">
         <v>-23254</v>
       </c>
@@ -7441,6 +7584,10 @@
         <f>IF(OR(K107="",G107=""),"",IF(G107&lt;=0,"",IFERROR(K107/G107-1,"")))</f>
         <v/>
       </c>
+      <c r="L108" s="17">
+        <f>IF(OR(L107="",H107=""),"",IF(H107&lt;=0,"",IFERROR(L107/H107-1,"")))</f>
+        <v/>
+      </c>
       <c r="S108" s="17">
         <f>IF(OR(S107="",R107=""),"",IF(R107&lt;=0,"",IFERROR(S107/R107-1,"")))</f>
         <v/>
@@ -7495,6 +7642,9 @@
       <c r="K109" s="22" t="n">
         <v>57660</v>
       </c>
+      <c r="L109" s="22" t="n">
+        <v>68012</v>
+      </c>
       <c r="S109" s="22" t="n">
         <v>-2138</v>
       </c>
@@ -7542,6 +7692,10 @@
         <f>IF(OR(K109="",G109=""),"",IF(K109*G109&lt;=0,"",IFERROR(K109/G109-1,"")))</f>
         <v/>
       </c>
+      <c r="L110" s="17">
+        <f>IF(OR(L109="",H109=""),"",IF(L109*H109&lt;=0,"",IFERROR(L109/H109-1,"")))</f>
+        <v/>
+      </c>
       <c r="S110" s="17">
         <f>IF(OR(S109="",R109=""),"",IF(S109*R109&lt;=0,"",IFERROR(S109/R109-1,"")))</f>
         <v/>
@@ -7596,6 +7750,9 @@
       <c r="K111" s="12" t="n">
         <v>139133</v>
       </c>
+      <c r="L111" s="12" t="n">
+        <v>159542</v>
+      </c>
       <c r="S111" s="12" t="n">
         <v>-21116</v>
       </c>
@@ -7643,6 +7800,10 @@
         <f>IF(OR(K111="",G111=""),"",IF(G111&lt;=0,"",IFERROR(K111/G111-1,"")))</f>
         <v/>
       </c>
+      <c r="L112" s="17">
+        <f>IF(OR(L111="",H111=""),"",IF(H111&lt;=0,"",IFERROR(L111/H111-1,"")))</f>
+        <v/>
+      </c>
       <c r="S112" s="17">
         <f>IF(OR(S111="",R111=""),"",IF(R111&lt;=0,"",IFERROR(S111/R111-1,"")))</f>
         <v/>
@@ -7697,6 +7858,9 @@
       <c r="K113" s="12" t="n">
         <v>139133</v>
       </c>
+      <c r="L113" s="12" t="n">
+        <v>159542</v>
+      </c>
       <c r="S113" s="12" t="n">
         <v>-21116</v>
       </c>
@@ -7742,6 +7906,10 @@
       </c>
       <c r="K114" s="17">
         <f>IF(OR(K113="",G113=""),"",IF(G113&lt;=0,"",IFERROR(K113/G113-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L114" s="17">
+        <f>IF(OR(L113="",H113=""),"",IF(H113&lt;=0,"",IFERROR(L113/H113-1,"")))</f>
         <v/>
       </c>
       <c r="S114" s="17">
@@ -7984,6 +8152,9 @@
       <c r="K118" s="12" t="n">
         <v>139133</v>
       </c>
+      <c r="L118" s="12" t="n">
+        <v>159542</v>
+      </c>
       <c r="S118" s="12" t="n">
         <v>-21116</v>
       </c>
@@ -8033,6 +8204,9 @@
       <c r="K119" s="22" t="n">
         <v>-543</v>
       </c>
+      <c r="L119" s="22" t="n">
+        <v>-6072</v>
+      </c>
       <c r="S119" s="22" t="n">
         <v>3438</v>
       </c>
@@ -8082,6 +8256,9 @@
       <c r="K120" s="22" t="n">
         <v>5363</v>
       </c>
+      <c r="L120" s="22" t="n">
+        <v>2754</v>
+      </c>
       <c r="S120" s="22" t="n">
         <v>-3023</v>
       </c>
@@ -8131,6 +8308,9 @@
       <c r="K121" s="22" t="n">
         <v>14</v>
       </c>
+      <c r="L121" s="22" t="n">
+        <v>4</v>
+      </c>
       <c r="S121" s="22" t="n">
         <v>14</v>
       </c>
@@ -8180,6 +8360,9 @@
       <c r="K122" s="22" t="n">
         <v>4833</v>
       </c>
+      <c r="L122" s="22" t="n">
+        <v>-3312</v>
+      </c>
       <c r="S122" s="22" t="n">
         <v>431</v>
       </c>
@@ -8229,6 +8412,9 @@
       <c r="K123" s="12" t="n">
         <v>143967</v>
       </c>
+      <c r="L123" s="12" t="n">
+        <v>156230</v>
+      </c>
       <c r="S123" s="12" t="n">
         <v>-20685</v>
       </c>
@@ -8277,6 +8463,9 @@
       </c>
       <c r="K124" s="12" t="n">
         <v>143967</v>
+      </c>
+      <c r="L124" s="12" t="n">
+        <v>156230</v>
       </c>
       <c r="S124" s="12" t="n">
         <v>-20685</v>
@@ -9128,7 +9317,7 @@
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Short Term Investment Securities Inv CF</t>
+          <t>유가증권 증감액(△는 증가)</t>
         </is>
       </c>
       <c r="F143" s="22" t="n">
@@ -9578,7 +9767,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6861 재무상태표</t>
+          <t>키엔스 재무상태표</t>
         </is>
       </c>
     </row>
@@ -9607,27 +9796,27 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>2027.2Q</t>
+          <t>2027.3Q</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -9682,19 +9871,19 @@
       </c>
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="11" t="n">
-        <v>1568423</v>
+        <v>1741736</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>1741736</v>
+        <v>1782006</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>1782006</v>
+        <v>1979505</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>1979505</v>
+        <v>1945636</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1945636</v>
+        <v>2079793</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1023426</v>
@@ -9720,19 +9909,19 @@
       </c>
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="21" t="n">
-        <v>489078</v>
+        <v>583276</v>
       </c>
       <c r="D6" s="22" t="n">
-        <v>583276</v>
+        <v>507115</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>507115</v>
+        <v>596976</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>596976</v>
+        <v>564751</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>564751</v>
+        <v>698507</v>
       </c>
       <c r="H6" s="21" t="n">
         <v>437675</v>
@@ -9758,19 +9947,19 @@
       </c>
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="21" t="n">
-        <v>675242</v>
+        <v>734575</v>
       </c>
       <c r="D7" s="22" t="n">
-        <v>734575</v>
+        <v>826897</v>
       </c>
       <c r="E7" s="22" t="n">
-        <v>826897</v>
+        <v>896913</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>896913</v>
+        <v>861843</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>861843</v>
+        <v>803618</v>
       </c>
       <c r="H7" s="21" t="n">
         <v>370055</v>
@@ -9796,19 +9985,19 @@
       </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="21" t="n">
-        <v>305063</v>
+        <v>324817</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>324817</v>
+        <v>342170</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>342170</v>
+        <v>379590</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>379590</v>
+        <v>397626</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>397626</v>
+        <v>438274</v>
       </c>
       <c r="H8" s="21" t="n">
         <v>160276</v>
@@ -9834,19 +10023,19 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="21" t="n">
-        <v>84903</v>
+        <v>83805</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>83805</v>
+        <v>87875</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>87875</v>
+        <v>85273</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>85273</v>
+        <v>101073</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>101073</v>
+        <v>117287</v>
       </c>
       <c r="H9" s="21" t="n">
         <v>34847</v>
@@ -9924,19 +10113,19 @@
       </c>
       <c r="B11" s="10" t="n"/>
       <c r="C11" s="11" t="n">
-        <v>1721430</v>
+        <v>1705655</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>1705655</v>
+        <v>1696638</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1696638</v>
+        <v>1691149</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1691149</v>
+        <v>1779255</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1779255</v>
+        <v>1875344</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>462796</v>
@@ -9962,19 +10151,19 @@
       </c>
       <c r="B12" s="10" t="n"/>
       <c r="C12" s="21" t="n">
-        <v>81515</v>
+        <v>82187</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>82187</v>
+        <v>84511</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>84511</v>
+        <v>94718</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>94718</v>
+        <v>98828</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>98828</v>
+        <v>99357</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>21426</v>
@@ -10000,19 +10189,19 @@
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="21" t="n">
-        <v>36111</v>
+        <v>33535</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>33535</v>
+        <v>31360</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>31360</v>
+        <v>29181</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>29181</v>
+        <v>26932</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>26932</v>
+        <v>24905</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>5204</v>
@@ -10108,19 +10297,19 @@
       </c>
       <c r="B16" s="10" t="n"/>
       <c r="C16" s="11" t="n">
-        <v>3289853</v>
+        <v>3447391</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>3447391</v>
+        <v>3478645</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3478645</v>
+        <v>3670655</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>3670655</v>
+        <v>3724891</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3724891</v>
+        <v>3955137</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>1486222</v>
@@ -10164,19 +10353,19 @@
       </c>
       <c r="B18" s="10" t="n"/>
       <c r="C18" s="11" t="n">
-        <v>114986</v>
+        <v>160696</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>160696</v>
+        <v>131496</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>131496</v>
+        <v>187831</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>187831</v>
+        <v>163958</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>163958</v>
+        <v>238325</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>97558</v>
@@ -10202,19 +10391,19 @@
       </c>
       <c r="B19" s="10" t="n"/>
       <c r="C19" s="21" t="n">
-        <v>15760</v>
+        <v>15091</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>15091</v>
+        <v>16653</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>16653</v>
+        <v>10890</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>10890</v>
+        <v>23600</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>23600</v>
+        <v>30907</v>
       </c>
       <c r="H19" s="21" t="n">
         <v>10645</v>
@@ -10328,19 +10517,19 @@
       </c>
       <c r="B23" s="10" t="n"/>
       <c r="C23" s="11" t="n">
-        <v>12015</v>
+        <v>11099</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>11099</v>
+        <v>11756</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>11756</v>
+        <v>11351</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>11351</v>
+        <v>12192</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>12192</v>
+        <v>11853</v>
       </c>
       <c r="H23" s="11" t="n">
         <v>7606</v>
@@ -10454,19 +10643,19 @@
       </c>
       <c r="B27" s="10" t="n"/>
       <c r="C27" s="11" t="n">
-        <v>127001</v>
+        <v>171795</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>171795</v>
+        <v>143253</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>143253</v>
+        <v>199183</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>199183</v>
+        <v>176150</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>176150</v>
+        <v>250179</v>
       </c>
       <c r="H27" s="11" t="n">
         <v>105164</v>
@@ -10614,19 +10803,19 @@
       </c>
       <c r="B31" s="10" t="n"/>
       <c r="C31" s="11" t="n">
-        <v>3162851</v>
+        <v>3275596</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>3275596</v>
+        <v>3335392</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>3335392</v>
+        <v>3471472</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>3471472</v>
+        <v>3548740</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>3548740</v>
+        <v>3704958</v>
       </c>
       <c r="H31" s="11" t="n">
         <v>1381057</v>
@@ -10690,19 +10879,19 @@
       </c>
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="21" t="n">
-        <v>3070209</v>
+        <v>3178052</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>3178052</v>
+        <v>3222567</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>3222567</v>
+        <v>3356584</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>3356584</v>
+        <v>3429023</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>3429023</v>
+        <v>3588565</v>
       </c>
       <c r="H33" s="21" t="n">
         <v>1316311</v>
@@ -10746,19 +10935,19 @@
       </c>
       <c r="B35" s="10" t="n"/>
       <c r="C35" s="11" t="n">
-        <v>3162851</v>
+        <v>3275596</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>3275596</v>
+        <v>3335392</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>3335392</v>
+        <v>3471472</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3471472</v>
+        <v>3548740</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3548740</v>
+        <v>3704958</v>
       </c>
       <c r="H35" s="11" t="n">
         <v>1381057</v>
@@ -10806,10 +10995,10 @@
       </c>
       <c r="B37" s="10" t="n"/>
       <c r="C37" s="11" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n">
+      <c r="D37" s="12" t="n">
         <v>409522</v>
       </c>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="11" t="n"/>
@@ -10838,10 +11027,10 @@
         </is>
       </c>
       <c r="C38" s="21" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n">
+      <c r="D38" s="22" t="n">
         <v>14342</v>
       </c>
+      <c r="E38" s="22" t="n"/>
       <c r="F38" s="22" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="21" t="n"/>
@@ -10918,10 +11107,10 @@
         </is>
       </c>
       <c r="C40" s="21" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n">
+      <c r="D40" s="22" t="n">
         <v>78820</v>
       </c>
+      <c r="E40" s="22" t="n"/>
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="21" t="n"/>
@@ -11250,23 +11439,23 @@
         </is>
       </c>
       <c r="C48" s="32">
-        <f>IFERROR((IF(COUNT('연간'!E19:H19)&lt;4,"",SUM('연간'!E19:H19)))/(IF(COUNT('연간'!E41:H41)&lt;4,"",SUM('연간'!E41:H41))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))/(IF(COUNT('연간'!F41:I41)&lt;4,"",SUM('연간'!F41:I41))),"")</f>
         <v/>
       </c>
       <c r="D48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))/(IF(COUNT('연간'!F41:I41)&lt;4,"",SUM('연간'!F41:I41))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))/(IF(COUNT('연간'!G41:J41)&lt;4,"",SUM('연간'!G41:J41))),"")</f>
         <v/>
       </c>
       <c r="E48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))/(IF(COUNT('연간'!G41:J41)&lt;4,"",SUM('연간'!G41:J41))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))/(IF(COUNT('연간'!H41:K41)&lt;4,"",SUM('연간'!H41:K41))),"")</f>
         <v/>
       </c>
       <c r="F48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))/(IF(COUNT('연간'!H41:K41)&lt;4,"",SUM('연간'!H41:K41))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))/(IF(COUNT('연간'!I41:L41)&lt;4,"",SUM('연간'!I41:L41))),"")</f>
         <v/>
       </c>
       <c r="G48" s="33">
-        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))/(IF(COUNT('연간'!I41:L41)&lt;4,"",SUM('연간'!I41:L41))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J19:M19)&lt;4,"",SUM('연간'!J19:M19)))/(IF(COUNT('연간'!J41:M41)&lt;4,"",SUM('연간'!J41:M41))),"")</f>
         <v/>
       </c>
       <c r="H48" s="32">
@@ -11302,23 +11491,23 @@
         </is>
       </c>
       <c r="C49" s="48">
-        <f>IFERROR(IF((IF(COUNT('연간'!E49:H49)&lt;4,"",SUM('연간'!E49:H49)))&lt;=0,"적자",C28/(IF(COUNT('연간'!E49:H49)&lt;4,"",SUM('연간'!E49:H49)))),"")</f>
+        <f>IFERROR(IF((IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))&lt;=0,"적자",C28/(IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))),"")</f>
         <v/>
       </c>
       <c r="D49" s="49">
-        <f>IFERROR(IF((IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))&lt;=0,"적자",D28/(IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))),"")</f>
+        <f>IFERROR(IF((IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))&lt;=0,"적자",D28/(IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))),"")</f>
         <v/>
       </c>
       <c r="E49" s="49">
-        <f>IFERROR(IF((IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))&lt;=0,"적자",E28/(IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))),"")</f>
+        <f>IFERROR(IF((IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))&lt;=0,"적자",E28/(IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))),"")</f>
         <v/>
       </c>
       <c r="F49" s="49">
-        <f>IFERROR(IF((IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))&lt;=0,"적자",F28/(IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))),"")</f>
+        <f>IFERROR(IF((IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))&lt;=0,"적자",F28/(IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))),"")</f>
         <v/>
       </c>
       <c r="G49" s="49">
-        <f>IFERROR(IF((IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))&lt;=0,"적자",G28/(IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))),"")</f>
+        <f>IFERROR(IF((IF(COUNT('연간'!J49:M49)&lt;4,"",SUM('연간'!J49:M49)))&lt;=0,"적자",G28/(IF(COUNT('연간'!J49:M49)&lt;4,"",SUM('연간'!J49:M49)))),"")</f>
         <v/>
       </c>
       <c r="H49" s="48">
@@ -11372,23 +11561,23 @@
         </is>
       </c>
       <c r="C51" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E49:H49)&lt;4,"",SUM('연간'!E49:H49)))/C31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))/C31,"")</f>
         <v/>
       </c>
       <c r="D51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49)))/D31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))/D31,"")</f>
         <v/>
       </c>
       <c r="E51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49)))/E31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))/E31,"")</f>
         <v/>
       </c>
       <c r="F51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49)))/F31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))/F31,"")</f>
         <v/>
       </c>
       <c r="G51" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49)))/G31,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J49:M49)&lt;4,"",SUM('연간'!J49:M49)))/G31,"")</f>
         <v/>
       </c>
       <c r="H51" s="37">
@@ -11424,23 +11613,23 @@
         </is>
       </c>
       <c r="C52" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E47:H47)&lt;4,"",SUM('연간'!E47:H47)))/C16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47)))/C16,"")</f>
         <v/>
       </c>
       <c r="D52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47)))/D16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))/D16,"")</f>
         <v/>
       </c>
       <c r="E52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))/E16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))/E16,"")</f>
         <v/>
       </c>
       <c r="F52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))/F16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))/F16,"")</f>
         <v/>
       </c>
       <c r="G52" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))/G16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))/G16,"")</f>
         <v/>
       </c>
       <c r="H52" s="37">
@@ -11476,23 +11665,23 @@
         </is>
       </c>
       <c r="C53" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E19:H19)&lt;4,"",SUM('연간'!E19:H19)))*(1-0.3)/(C35+C29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))*(1-0.3)/(C35+C29),"")</f>
         <v/>
       </c>
       <c r="D53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))*(1-0.3)/(D35+D29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))*(1-0.3)/(D35+D29),"")</f>
         <v/>
       </c>
       <c r="E53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))*(1-0.3)/(E35+E29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))*(1-0.3)/(E35+E29),"")</f>
         <v/>
       </c>
       <c r="F53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))*(1-0.3)/(F35+F29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))*(1-0.3)/(F35+F29),"")</f>
         <v/>
       </c>
       <c r="G53" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))*(1-0.3)/(G35+G29),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J19:M19)&lt;4,"",SUM('연간'!J19:M19)))*(1-0.3)/(G35+G29),"")</f>
         <v/>
       </c>
       <c r="H53" s="37">
@@ -11528,23 +11717,23 @@
         </is>
       </c>
       <c r="C54" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E13:H13)&lt;4,"",SUM('연간'!E13:H13)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F13:I13)&lt;4,"",SUM('연간'!F13:I13)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
         <v/>
       </c>
       <c r="D54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F13:I13)&lt;4,"",SUM('연간'!F13:I13)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G13:J13)&lt;4,"",SUM('연간'!G13:J13)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="E54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G13:J13)&lt;4,"",SUM('연간'!G13:J13)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H13:K13)&lt;4,"",SUM('연간'!H13:K13)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="F54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H13:K13)&lt;4,"",SUM('연간'!H13:K13)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I13:L13)&lt;4,"",SUM('연간'!I13:L13)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="G54" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I13:L13)&lt;4,"",SUM('연간'!I13:L13)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J13:M13)&lt;4,"",SUM('연간'!J13:M13)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="H54" s="37">
@@ -11580,23 +11769,23 @@
         </is>
       </c>
       <c r="C55" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E19:H19)&lt;4,"",SUM('연간'!E19:H19)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
         <v/>
       </c>
       <c r="D55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F19:I19)&lt;4,"",SUM('연간'!F19:I19)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="E55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G19:J19)&lt;4,"",SUM('연간'!G19:J19)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="F55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H19:K19)&lt;4,"",SUM('연간'!H19:K19)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="G55" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I19:L19)&lt;4,"",SUM('연간'!I19:L19)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J19:M19)&lt;4,"",SUM('연간'!J19:M19)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="H55" s="37">
@@ -11632,23 +11821,23 @@
         </is>
       </c>
       <c r="C56" s="37">
-        <f>IFERROR((IF(COUNT('연간'!E47:H47)&lt;4,"",SUM('연간'!E47:H47)))/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
         <v/>
       </c>
       <c r="D56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47)))/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
         <v/>
       </c>
       <c r="E56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47)))/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
         <v/>
       </c>
       <c r="F56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47)))/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
         <v/>
       </c>
       <c r="G56" s="38">
-        <f>IFERROR((IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47)))/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47)))/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),"")</f>
         <v/>
       </c>
       <c r="H56" s="37">
@@ -11702,23 +11891,23 @@
         </is>
       </c>
       <c r="C58" s="32">
-        <f>IFERROR((IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4)))/C16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))/C16,"")</f>
         <v/>
       </c>
       <c r="D58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))/D16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))/D16,"")</f>
         <v/>
       </c>
       <c r="E58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))/E16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))/E16,"")</f>
         <v/>
       </c>
       <c r="F58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))/F16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))/F16,"")</f>
         <v/>
       </c>
       <c r="G58" s="33">
-        <f>IFERROR((IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))/G16,"")</f>
+        <f>IFERROR((IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))/G16,"")</f>
         <v/>
       </c>
       <c r="H58" s="32">
@@ -11754,23 +11943,23 @@
         </is>
       </c>
       <c r="C59" s="50">
-        <f>IFERROR(C8/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4)))*365,"")</f>
+        <f>IFERROR(C8/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))*365,"")</f>
         <v/>
       </c>
       <c r="D59" s="51">
-        <f>IFERROR(D8/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4)))*365,"")</f>
+        <f>IFERROR(D8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
       <c r="E59" s="51">
-        <f>IFERROR(E8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
+        <f>IFERROR(E8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
       <c r="F59" s="51">
-        <f>IFERROR(F8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
+        <f>IFERROR(F8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
       <c r="G59" s="51">
-        <f>IFERROR(G8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
+        <f>IFERROR(G8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
       <c r="H59" s="50">
@@ -11806,23 +11995,23 @@
         </is>
       </c>
       <c r="C60" s="50">
-        <f>IFERROR(C9/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
+        <f>IFERROR(C9/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
         <v/>
       </c>
       <c r="D60" s="51">
-        <f>IFERROR(D9/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
+        <f>IFERROR(D9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
       <c r="E60" s="51">
-        <f>IFERROR(E9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
+        <f>IFERROR(E9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
       <c r="F60" s="51">
-        <f>IFERROR(F9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
+        <f>IFERROR(F9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
       <c r="G60" s="51">
-        <f>IFERROR(G9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
+        <f>IFERROR(G9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
       <c r="H60" s="50">
@@ -11858,23 +12047,23 @@
         </is>
       </c>
       <c r="C61" s="50">
-        <f>IFERROR(C19/(IF(COUNT('연간'!E11:H11)&lt;4,"",SUM('연간'!E11:H11)))*365,"")</f>
+        <f>IFERROR(C19/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
         <v/>
       </c>
       <c r="D61" s="51">
-        <f>IFERROR(D19/(IF(COUNT('연간'!F11:I11)&lt;4,"",SUM('연간'!F11:I11)))*365,"")</f>
+        <f>IFERROR(D19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
       <c r="E61" s="51">
-        <f>IFERROR(E19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
+        <f>IFERROR(E19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
       <c r="F61" s="51">
-        <f>IFERROR(F19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
+        <f>IFERROR(F19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
       <c r="G61" s="51">
-        <f>IFERROR(G19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
+        <f>IFERROR(G19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
       <c r="H61" s="50">
@@ -11980,23 +12169,23 @@
         </is>
       </c>
       <c r="C64" s="32">
-        <f>IF(C37="","",IFERROR(C37/(IF(COUNT('연간'!E47:H47)&lt;4,"",SUM('연간'!E47:H47))),""))</f>
+        <f>IF(C37="","",IFERROR(C37/(IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47))),""))</f>
         <v/>
       </c>
       <c r="D64" s="33">
-        <f>IF(D37="","",IFERROR(D37/(IF(COUNT('연간'!F47:I47)&lt;4,"",SUM('연간'!F47:I47))),""))</f>
+        <f>IF(D37="","",IFERROR(D37/(IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47))),""))</f>
         <v/>
       </c>
       <c r="E64" s="33">
-        <f>IF(E37="","",IFERROR(E37/(IF(COUNT('연간'!G47:J47)&lt;4,"",SUM('연간'!G47:J47))),""))</f>
+        <f>IF(E37="","",IFERROR(E37/(IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47))),""))</f>
         <v/>
       </c>
       <c r="F64" s="33">
-        <f>IF(F37="","",IFERROR(F37/(IF(COUNT('연간'!H47:K47)&lt;4,"",SUM('연간'!H47:K47))),""))</f>
+        <f>IF(F37="","",IFERROR(F37/(IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47))),""))</f>
         <v/>
       </c>
       <c r="G64" s="33">
-        <f>IF(G37="","",IFERROR(G37/(IF(COUNT('연간'!I47:L47)&lt;4,"",SUM('연간'!I47:L47))),""))</f>
+        <f>IF(G37="","",IFERROR(G37/(IF(COUNT('연간'!J47:M47)&lt;4,"",SUM('연간'!J47:M47))),""))</f>
         <v/>
       </c>
       <c r="H64" s="32">
@@ -12032,23 +12221,23 @@
         </is>
       </c>
       <c r="C65" s="37">
-        <f>IF(C39="","",IFERROR(C39/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),""))</f>
+        <f>IF(C39="","",IFERROR(C39/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
         <v/>
       </c>
       <c r="D65" s="38">
-        <f>IF(D39="","",IFERROR(D39/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
+        <f>IF(D39="","",IFERROR(D39/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
         <v/>
       </c>
       <c r="E65" s="38">
-        <f>IF(E39="","",IFERROR(E39/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
+        <f>IF(E39="","",IFERROR(E39/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
         <v/>
       </c>
       <c r="F65" s="38">
-        <f>IF(F39="","",IFERROR(F39/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
+        <f>IF(F39="","",IFERROR(F39/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
         <v/>
       </c>
       <c r="G65" s="38">
-        <f>IF(G39="","",IFERROR(G39/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
+        <f>IF(G39="","",IFERROR(G39/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),""))</f>
         <v/>
       </c>
       <c r="H65" s="37">
@@ -12084,23 +12273,23 @@
         </is>
       </c>
       <c r="C66" s="37">
-        <f>IF(C38="","",IFERROR(C38/(IF(COUNT('연간'!E4:H4)&lt;4,"",SUM('연간'!E4:H4))),""))</f>
+        <f>IF(C38="","",IFERROR(C38/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
         <v/>
       </c>
       <c r="D66" s="38">
-        <f>IF(D38="","",IFERROR(D38/(IF(COUNT('연간'!F4:I4)&lt;4,"",SUM('연간'!F4:I4))),""))</f>
+        <f>IF(D38="","",IFERROR(D38/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
         <v/>
       </c>
       <c r="E66" s="38">
-        <f>IF(E38="","",IFERROR(E38/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4))),""))</f>
+        <f>IF(E38="","",IFERROR(E38/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
         <v/>
       </c>
       <c r="F66" s="38">
-        <f>IF(F38="","",IFERROR(F38/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4))),""))</f>
+        <f>IF(F38="","",IFERROR(F38/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
         <v/>
       </c>
       <c r="G66" s="38">
-        <f>IF(G38="","",IFERROR(G38/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4))),""))</f>
+        <f>IF(G38="","",IFERROR(G38/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4))),""))</f>
         <v/>
       </c>
       <c r="H66" s="37">
@@ -12136,23 +12325,23 @@
         </is>
       </c>
       <c r="C67" s="37">
-        <f>IF(C40="","",IFERROR(C40/(IF(COUNT('연간'!E49:H49)&lt;4,"",SUM('연간'!E49:H49))),""))</f>
+        <f>IF(C40="","",IFERROR(C40/(IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49))),""))</f>
         <v/>
       </c>
       <c r="D67" s="38">
-        <f>IF(D40="","",IFERROR(D40/(IF(COUNT('연간'!F49:I49)&lt;4,"",SUM('연간'!F49:I49))),""))</f>
+        <f>IF(D40="","",IFERROR(D40/(IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49))),""))</f>
         <v/>
       </c>
       <c r="E67" s="38">
-        <f>IF(E40="","",IFERROR(E40/(IF(COUNT('연간'!G49:J49)&lt;4,"",SUM('연간'!G49:J49))),""))</f>
+        <f>IF(E40="","",IFERROR(E40/(IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49))),""))</f>
         <v/>
       </c>
       <c r="F67" s="38">
-        <f>IF(F40="","",IFERROR(F40/(IF(COUNT('연간'!H49:K49)&lt;4,"",SUM('연간'!H49:K49))),""))</f>
+        <f>IF(F40="","",IFERROR(F40/(IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49))),""))</f>
         <v/>
       </c>
       <c r="G67" s="38">
-        <f>IF(G40="","",IFERROR(G40/(IF(COUNT('연간'!I49:L49)&lt;4,"",SUM('연간'!I49:L49))),""))</f>
+        <f>IF(G40="","",IFERROR(G40/(IF(COUNT('연간'!J49:M49)&lt;4,"",SUM('연간'!J49:M49))),""))</f>
         <v/>
       </c>
       <c r="H67" s="37">
@@ -12211,27 +12400,27 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2026.2Q</t>
+          <t>2026.3Q</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>2026.3Q</t>
+          <t>2026.4Q</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>2026.4Q</t>
+          <t>2027.1Q</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>2027.1Q</t>
+          <t>2027.2Q</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>2027.2Q</t>
+          <t>2027.3Q</t>
         </is>
       </c>
       <c r="H70" s="5" t="inlineStr">
@@ -12267,19 +12456,19 @@
         </is>
       </c>
       <c r="C71" s="22" t="n">
-        <v>489078</v>
+        <v>583276</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>583276</v>
+        <v>507115</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>507115</v>
+        <v>596976</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>596976</v>
+        <v>564751</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>564751</v>
+        <v>698507</v>
       </c>
       <c r="H71" s="22" t="n">
         <v>437675</v>
@@ -12304,19 +12493,19 @@
         </is>
       </c>
       <c r="C72" s="22" t="n">
-        <v>305063</v>
+        <v>324817</v>
       </c>
       <c r="D72" s="22" t="n">
-        <v>324817</v>
+        <v>342170</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>342170</v>
+        <v>379590</v>
       </c>
       <c r="F72" s="22" t="n">
-        <v>379590</v>
+        <v>397626</v>
       </c>
       <c r="G72" s="22" t="n">
-        <v>397626</v>
+        <v>438274</v>
       </c>
       <c r="H72" s="22" t="n">
         <v>160276</v>
@@ -12341,19 +12530,19 @@
         </is>
       </c>
       <c r="C73" s="22" t="n">
-        <v>675242</v>
+        <v>734575</v>
       </c>
       <c r="D73" s="22" t="n">
-        <v>734575</v>
+        <v>826897</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>826897</v>
+        <v>896913</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>896913</v>
+        <v>861843</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>861843</v>
+        <v>803618</v>
       </c>
       <c r="H73" s="22" t="n">
         <v>370055</v>
@@ -12378,19 +12567,19 @@
         </is>
       </c>
       <c r="C74" s="22" t="n">
-        <v>84903</v>
+        <v>83805</v>
       </c>
       <c r="D74" s="22" t="n">
-        <v>83805</v>
+        <v>87875</v>
       </c>
       <c r="E74" s="22" t="n">
-        <v>87875</v>
+        <v>85273</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>85273</v>
+        <v>101073</v>
       </c>
       <c r="G74" s="22" t="n">
-        <v>101073</v>
+        <v>117287</v>
       </c>
       <c r="H74" s="22" t="n">
         <v>34847</v>
@@ -12425,19 +12614,19 @@
         </is>
       </c>
       <c r="C76" s="22" t="n">
-        <v>15866</v>
+        <v>17052</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>17052</v>
+        <v>19855</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>19855</v>
+        <v>22887</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>22887</v>
+        <v>22783</v>
       </c>
       <c r="G76" s="22" t="n">
-        <v>22783</v>
+        <v>24579</v>
       </c>
       <c r="H76" s="22" t="n">
         <v>6543</v>
@@ -12462,19 +12651,19 @@
         </is>
       </c>
       <c r="C77" s="22" t="n">
-        <v>-1731</v>
+        <v>-1791</v>
       </c>
       <c r="D77" s="22" t="n">
-        <v>-1791</v>
+        <v>-1907</v>
       </c>
       <c r="E77" s="22" t="n">
-        <v>-1907</v>
+        <v>-2135</v>
       </c>
       <c r="F77" s="22" t="n">
-        <v>-2135</v>
+        <v>-2441</v>
       </c>
       <c r="G77" s="22" t="n">
-        <v>-2441</v>
+        <v>-2473</v>
       </c>
       <c r="H77" s="22" t="n">
         <v>-366</v>
@@ -12499,19 +12688,19 @@
         </is>
       </c>
       <c r="C78" s="12" t="n">
-        <v>1568423</v>
+        <v>1741736</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>1741736</v>
+        <v>1782006</v>
       </c>
       <c r="E78" s="12" t="n">
-        <v>1782006</v>
+        <v>1979505</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>1979505</v>
+        <v>1945636</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>1945636</v>
+        <v>2079793</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>1023426</v>
@@ -12535,7 +12724,7 @@
           <t>건물·구축물</t>
         </is>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="E79" s="22" t="n">
         <v>34915</v>
       </c>
       <c r="H79" s="22" t="n">
@@ -12548,7 +12737,7 @@
           <t>감가상각누계액</t>
         </is>
       </c>
-      <c r="F80" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>-22804</v>
       </c>
       <c r="H80" s="22" t="n">
@@ -12561,7 +12750,7 @@
           <t>건물·구축물(순액)</t>
         </is>
       </c>
-      <c r="F81" s="22" t="n">
+      <c r="E81" s="22" t="n">
         <v>12110</v>
       </c>
       <c r="H81" s="22" t="n">
@@ -12574,7 +12763,7 @@
           <t>공구·기구·비품</t>
         </is>
       </c>
-      <c r="F82" s="22" t="n">
+      <c r="E82" s="22" t="n">
         <v>75596</v>
       </c>
       <c r="H82" s="22" t="n">
@@ -12587,7 +12776,7 @@
           <t>감가상각누계액</t>
         </is>
       </c>
-      <c r="F83" s="22" t="n">
+      <c r="E83" s="22" t="n">
         <v>-61193</v>
       </c>
       <c r="H83" s="22" t="n">
@@ -12600,7 +12789,7 @@
           <t>공구·기구·비품(순액)</t>
         </is>
       </c>
-      <c r="F84" s="22" t="n">
+      <c r="E84" s="22" t="n">
         <v>14403</v>
       </c>
       <c r="H84" s="22" t="n">
@@ -12613,7 +12802,7 @@
           <t>토지</t>
         </is>
       </c>
-      <c r="F85" s="22" t="n">
+      <c r="E85" s="22" t="n">
         <v>32971</v>
       </c>
       <c r="H85" s="22" t="n">
@@ -12626,7 +12815,7 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="F86" s="22" t="n">
+      <c r="E86" s="22" t="n">
         <v>55809</v>
       </c>
       <c r="H86" s="22" t="n">
@@ -12639,7 +12828,7 @@
           <t>감가상각누계액</t>
         </is>
       </c>
-      <c r="F87" s="22" t="n">
+      <c r="E87" s="22" t="n">
         <v>-20576</v>
       </c>
       <c r="H87" s="22" t="n">
@@ -12652,7 +12841,7 @@
           <t>기타(순액)</t>
         </is>
       </c>
-      <c r="F88" s="22" t="n">
+      <c r="E88" s="22" t="n">
         <v>35232</v>
       </c>
       <c r="H88" s="22" t="n">
@@ -12666,19 +12855,19 @@
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>81515</v>
+        <v>82187</v>
       </c>
       <c r="D89" s="22" t="n">
-        <v>82187</v>
+        <v>84511</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>84511</v>
+        <v>94718</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>94718</v>
+        <v>98828</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>98828</v>
+        <v>99357</v>
       </c>
       <c r="H89" s="22" t="n">
         <v>21426</v>
@@ -12702,7 +12891,7 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="F90" s="22" t="n">
+      <c r="E90" s="22" t="n">
         <v>29181</v>
       </c>
       <c r="H90" s="22" t="n">
@@ -12716,19 +12905,19 @@
         </is>
       </c>
       <c r="C91" s="22" t="n">
-        <v>36111</v>
+        <v>33535</v>
       </c>
       <c r="D91" s="22" t="n">
-        <v>33535</v>
+        <v>31360</v>
       </c>
       <c r="E91" s="22" t="n">
-        <v>31360</v>
+        <v>29181</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>29181</v>
+        <v>26932</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>26932</v>
+        <v>24905</v>
       </c>
       <c r="H91" s="22" t="n">
         <v>5204</v>
@@ -12753,19 +12942,19 @@
         </is>
       </c>
       <c r="C92" s="22" t="n">
-        <v>1559662</v>
+        <v>1544666</v>
       </c>
       <c r="D92" s="22" t="n">
-        <v>1544666</v>
+        <v>1531075</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>1531075</v>
+        <v>1514304</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>1514304</v>
+        <v>1598277</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>1598277</v>
+        <v>1691841</v>
       </c>
       <c r="H92" s="22" t="n">
         <v>432981</v>
@@ -12796,23 +12985,23 @@
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>Long Term Time Deposits IOA</t>
+          <t>장기성 예금</t>
         </is>
       </c>
       <c r="C94" s="22" t="n">
-        <v>17992</v>
+        <v>18861</v>
       </c>
       <c r="D94" s="22" t="n">
-        <v>18861</v>
+        <v>19976</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>19976</v>
+        <v>20220</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>20220</v>
+        <v>20422</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>20422</v>
+        <v>20405</v>
       </c>
       <c r="I94" s="22" t="n">
         <v>15793</v>
@@ -12833,7 +13022,7 @@
           <t>이연법인세자산</t>
         </is>
       </c>
-      <c r="F95" s="22" t="n">
+      <c r="E95" s="22" t="n">
         <v>20515</v>
       </c>
     </row>
@@ -12844,19 +13033,19 @@
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>26208</v>
+        <v>26465</v>
       </c>
       <c r="D96" s="22" t="n">
-        <v>26465</v>
+        <v>29775</v>
       </c>
       <c r="E96" s="22" t="n">
-        <v>29775</v>
+        <v>32786</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>32786</v>
+        <v>34854</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>34854</v>
+        <v>38834</v>
       </c>
       <c r="H96" s="22" t="n">
         <v>2790</v>
@@ -12893,7 +13082,7 @@
         <v>-60</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="H97" s="22" t="n">
         <v>-61</v>
@@ -12918,19 +13107,19 @@
         </is>
       </c>
       <c r="C98" s="22" t="n">
-        <v>1603803</v>
+        <v>1589932</v>
       </c>
       <c r="D98" s="22" t="n">
-        <v>1589932</v>
+        <v>1580766</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>1580766</v>
+        <v>1567250</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>1567250</v>
+        <v>1653494</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>1653494</v>
+        <v>1751081</v>
       </c>
       <c r="H98" s="22" t="n">
         <v>436165</v>
@@ -12955,19 +13144,19 @@
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>1721430</v>
+        <v>1705655</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>1705655</v>
+        <v>1696638</v>
       </c>
       <c r="E99" s="12" t="n">
-        <v>1696638</v>
+        <v>1691149</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>1691149</v>
+        <v>1779255</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>1779255</v>
+        <v>1875344</v>
       </c>
       <c r="H99" s="12" t="n">
         <v>462796</v>
@@ -12992,19 +13181,19 @@
         </is>
       </c>
       <c r="C100" s="12" t="n">
-        <v>3289853</v>
+        <v>3447391</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>3447391</v>
+        <v>3478645</v>
       </c>
       <c r="E100" s="12" t="n">
-        <v>3478645</v>
+        <v>3670655</v>
       </c>
       <c r="F100" s="12" t="n">
-        <v>3670655</v>
+        <v>3724891</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>3724891</v>
+        <v>3955137</v>
       </c>
       <c r="H100" s="12" t="n">
         <v>1486222</v>
@@ -13029,19 +13218,19 @@
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>15760</v>
+        <v>15091</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>15091</v>
+        <v>16653</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>16653</v>
+        <v>10890</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>10890</v>
+        <v>23600</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>23600</v>
+        <v>30907</v>
       </c>
       <c r="H101" s="22" t="n">
         <v>10645</v>
@@ -13066,19 +13255,19 @@
         </is>
       </c>
       <c r="C102" s="22" t="n">
-        <v>38541</v>
+        <v>80769</v>
       </c>
       <c r="D102" s="22" t="n">
-        <v>80769</v>
+        <v>46157</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>46157</v>
+        <v>102331</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>102331</v>
+        <v>59945</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>59945</v>
+        <v>121009</v>
       </c>
       <c r="H102" s="22" t="n">
         <v>58799</v>
@@ -13103,19 +13292,19 @@
         </is>
       </c>
       <c r="C103" s="22" t="n">
-        <v>15282</v>
+        <v>19126</v>
       </c>
       <c r="D103" s="22" t="n">
-        <v>19126</v>
+        <v>17097</v>
       </c>
       <c r="E103" s="22" t="n">
-        <v>17097</v>
+        <v>22271</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>22271</v>
+        <v>21315</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>21315</v>
+        <v>28583</v>
       </c>
       <c r="H103" s="22" t="n">
         <v>10131</v>
@@ -13140,19 +13329,19 @@
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>45401</v>
+        <v>45708</v>
       </c>
       <c r="D104" s="22" t="n">
-        <v>45708</v>
+        <v>51588</v>
       </c>
       <c r="E104" s="22" t="n">
-        <v>51588</v>
+        <v>52338</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>52338</v>
+        <v>59096</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>59096</v>
+        <v>57824</v>
       </c>
       <c r="H104" s="22" t="n">
         <v>17982</v>
@@ -13177,19 +13366,19 @@
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>114986</v>
+        <v>160696</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>160696</v>
+        <v>131496</v>
       </c>
       <c r="E105" s="12" t="n">
-        <v>131496</v>
+        <v>187831</v>
       </c>
       <c r="F105" s="12" t="n">
-        <v>187831</v>
+        <v>163958</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>163958</v>
+        <v>238325</v>
       </c>
       <c r="H105" s="12" t="n">
         <v>97558</v>
@@ -13213,7 +13402,7 @@
           <t>기타</t>
         </is>
       </c>
-      <c r="F106" s="22" t="n">
+      <c r="E106" s="22" t="n">
         <v>11351</v>
       </c>
       <c r="H106" s="22" t="n">
@@ -13227,19 +13416,19 @@
         </is>
       </c>
       <c r="C107" s="12" t="n">
-        <v>12015</v>
+        <v>11099</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>11099</v>
+        <v>11756</v>
       </c>
       <c r="E107" s="12" t="n">
-        <v>11756</v>
+        <v>11351</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>11351</v>
+        <v>12192</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>12192</v>
+        <v>11853</v>
       </c>
       <c r="H107" s="12" t="n">
         <v>7606</v>
@@ -13264,19 +13453,19 @@
         </is>
       </c>
       <c r="C108" s="12" t="n">
-        <v>127001</v>
+        <v>171795</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>171795</v>
+        <v>143253</v>
       </c>
       <c r="E108" s="12" t="n">
-        <v>143253</v>
+        <v>199183</v>
       </c>
       <c r="F108" s="12" t="n">
-        <v>199183</v>
+        <v>176150</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>176150</v>
+        <v>250179</v>
       </c>
       <c r="H108" s="12" t="n">
         <v>105164</v>
@@ -13341,7 +13530,7 @@
         <v>30541</v>
       </c>
       <c r="D110" s="22" t="n">
-        <v>30541</v>
+        <v>30544</v>
       </c>
       <c r="E110" s="22" t="n">
         <v>30544</v>
@@ -13375,19 +13564,19 @@
         </is>
       </c>
       <c r="C111" s="22" t="n">
-        <v>3070209</v>
+        <v>3178052</v>
       </c>
       <c r="D111" s="22" t="n">
-        <v>3178052</v>
+        <v>3222567</v>
       </c>
       <c r="E111" s="22" t="n">
-        <v>3222567</v>
+        <v>3356584</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>3356584</v>
+        <v>3429023</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>3429023</v>
+        <v>3588565</v>
       </c>
       <c r="H111" s="22" t="n">
         <v>1316311</v>
@@ -13412,19 +13601,19 @@
         </is>
       </c>
       <c r="C112" s="22" t="n">
-        <v>-3840</v>
+        <v>-3847</v>
       </c>
       <c r="D112" s="22" t="n">
-        <v>-3847</v>
+        <v>-3850</v>
       </c>
       <c r="E112" s="22" t="n">
-        <v>-3850</v>
+        <v>-3854</v>
       </c>
       <c r="F112" s="22" t="n">
-        <v>-3854</v>
+        <v>-3858</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>-3858</v>
+        <v>-3870</v>
       </c>
       <c r="H112" s="22" t="n">
         <v>-3658</v>
@@ -13449,19 +13638,19 @@
         </is>
       </c>
       <c r="C113" s="12" t="n">
-        <v>3127547</v>
+        <v>3235384</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>3235384</v>
+        <v>3279898</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>3279898</v>
+        <v>3413911</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>3413911</v>
+        <v>3486346</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>3486346</v>
+        <v>3645876</v>
       </c>
       <c r="H113" s="12" t="n">
         <v>1373828</v>
@@ -13486,19 +13675,19 @@
         </is>
       </c>
       <c r="C114" s="22" t="n">
-        <v>-3874</v>
+        <v>-6988</v>
       </c>
       <c r="D114" s="22" t="n">
-        <v>-6988</v>
+        <v>-10523</v>
       </c>
       <c r="E114" s="22" t="n">
-        <v>-10523</v>
+        <v>-11843</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>-11843</v>
+        <v>-12387</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>-12387</v>
+        <v>-18458</v>
       </c>
       <c r="H114" s="22" t="n">
         <v>3648</v>
@@ -13523,19 +13712,19 @@
         </is>
       </c>
       <c r="C115" s="22" t="n">
-        <v>39182</v>
+        <v>47204</v>
       </c>
       <c r="D115" s="22" t="n">
-        <v>47204</v>
+        <v>66020</v>
       </c>
       <c r="E115" s="22" t="n">
-        <v>66020</v>
+        <v>69406</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>69406</v>
+        <v>74783</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>74783</v>
+        <v>77539</v>
       </c>
       <c r="H115" s="22" t="n">
         <v>3563</v>
@@ -13560,7 +13749,7 @@
         </is>
       </c>
       <c r="C116" s="22" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="D116" s="22" t="n">
         <v>-3</v>
@@ -13569,10 +13758,10 @@
         <v>-3</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H116" s="22" t="n">
         <v>17</v>
@@ -13597,19 +13786,19 @@
         </is>
       </c>
       <c r="C117" s="22" t="n">
-        <v>35304</v>
+        <v>40212</v>
       </c>
       <c r="D117" s="22" t="n">
-        <v>40212</v>
+        <v>55493</v>
       </c>
       <c r="E117" s="22" t="n">
-        <v>55493</v>
+        <v>57560</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>57560</v>
+        <v>62394</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>62394</v>
+        <v>59081</v>
       </c>
       <c r="H117" s="22" t="n">
         <v>7228</v>
@@ -13634,19 +13823,19 @@
         </is>
       </c>
       <c r="C118" s="12" t="n">
-        <v>3162851</v>
+        <v>3275596</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>3275596</v>
+        <v>3335392</v>
       </c>
       <c r="E118" s="12" t="n">
-        <v>3335392</v>
+        <v>3471472</v>
       </c>
       <c r="F118" s="12" t="n">
-        <v>3471472</v>
+        <v>3548740</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>3548740</v>
+        <v>3704958</v>
       </c>
       <c r="H118" s="12" t="n">
         <v>1381057</v>
@@ -13671,19 +13860,19 @@
         </is>
       </c>
       <c r="C119" s="12" t="n">
-        <v>3289853</v>
+        <v>3447391</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>3447391</v>
+        <v>3478645</v>
       </c>
       <c r="E119" s="12" t="n">
-        <v>3478645</v>
+        <v>3670655</v>
       </c>
       <c r="F119" s="12" t="n">
-        <v>3670655</v>
+        <v>3724891</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>3724891</v>
+        <v>3955137</v>
       </c>
       <c r="H119" s="12" t="n">
         <v>1486222</v>
@@ -13788,6 +13977,1423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="52" t="inlineStr">
+        <is>
+          <t>키엔스 섹터·사업 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="53" t="inlineStr">
+        <is>
+          <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>GP A</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C5" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="56" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="B6" s="57" t="n">
+        <v>6211.9</v>
+      </c>
+      <c r="C6" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="56" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B7" s="57" t="n">
+        <v>7547.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="56" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="B8" s="57" t="n">
+        <v>8025.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="56" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="B9" s="57" t="n">
+        <v>8877</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="56" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B10" s="57" t="n">
+        <v>9707.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>SGA A</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C13" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="56" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="n">
+        <v>2031.5</v>
+      </c>
+      <c r="C14" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="56" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n">
+        <v>2558.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>3074.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="56" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="n">
+        <v>3379.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="56" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="n">
+        <v>3749.8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>CONS FY</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C21" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="n">
+        <v>14502.2</v>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B23" s="57" t="n">
+        <v>2336.73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>EPS hi</t>
+        </is>
+      </c>
+      <c r="B25" s="57" t="n">
+        <v>2497.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>EPS lo</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="n">
+        <v>2167.97</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>eps90</t>
+        </is>
+      </c>
+      <c r="B27" s="57" t="n">
+        <v>2122.67</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>CONS 2Q</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="n">
+        <v>3631.8</v>
+      </c>
+      <c r="C31" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="56" t="inlineStr">
+        <is>
+          <t>매출 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B32" s="59" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="56" t="inlineStr">
+        <is>
+          <t>매출 lo</t>
+        </is>
+      </c>
+      <c r="B33" s="57" t="n">
+        <v>3506.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="56" t="inlineStr">
+        <is>
+          <t>매출 hi</t>
+        </is>
+      </c>
+      <c r="B34" s="57" t="n">
+        <v>3733.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B35" s="57" t="n">
+        <v>635.85</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>EPS 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B36" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>EPS lo</t>
+        </is>
+      </c>
+      <c r="B37" s="57" t="n">
+        <v>533.76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>EPS hi</t>
+        </is>
+      </c>
+      <c r="B38" s="57" t="n">
+        <v>737.9400000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B39" s="57" t="n">
+        <v>1542.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="54" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="B41" s="54" t="n"/>
+      <c r="C41" s="54" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C42" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="56" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="B43" s="59" t="n">
+        <v>97800</v>
+      </c>
+      <c r="C43" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>중앙값</t>
+        </is>
+      </c>
+      <c r="B44" s="59" t="n">
+        <v>95500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="B45" s="59" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>lo</t>
+        </is>
+      </c>
+      <c r="B46" s="59" t="n">
+        <v>77000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B47" s="59" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="54" t="inlineStr">
+        <is>
+          <t>OVS</t>
+        </is>
+      </c>
+      <c r="B49" s="54" t="n"/>
+      <c r="C49" s="54" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B50" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B51" s="57" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="C51" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B52" s="57" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B53" s="57" t="n">
+        <v>67.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="B54" s="57" t="n">
+        <v>64.40000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="B55" s="57" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B56" s="57" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="54" t="inlineStr">
+        <is>
+          <t>연구개발비</t>
+        </is>
+      </c>
+      <c r="B58" s="54" t="n"/>
+      <c r="C58" s="54" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B59" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C59" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B60" s="59" t="n">
+        <v>76</v>
+      </c>
+      <c r="C60" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B61" s="59" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B62" s="59" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B63" s="59" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="B64" s="59" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="B65" s="59" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="B66" s="59" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B67" s="59" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="54" t="inlineStr">
+        <is>
+          <t>설비투자</t>
+        </is>
+      </c>
+      <c r="B69" s="54" t="n"/>
+      <c r="C69" s="54" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B70" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B71" s="59" t="n">
+        <v>42</v>
+      </c>
+      <c r="C71" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B72" s="59" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B73" s="59" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B74" s="59" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="B75" s="59" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="B76" s="59" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="B77" s="59" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B78" s="59" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="54" t="inlineStr">
+        <is>
+          <t>환율 · 달러</t>
+        </is>
+      </c>
+      <c r="B80" s="54" t="n"/>
+      <c r="C80" s="54" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B81" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C81" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="56" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="B82" s="57" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="C82" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="56" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="B83" s="57" t="n">
+        <v>159.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="56" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="B84" s="57" t="n">
+        <v>159.8</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="54" t="inlineStr">
+        <is>
+          <t>환율 · 유로</t>
+        </is>
+      </c>
+      <c r="B86" s="54" t="n"/>
+      <c r="C86" s="54" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B87" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C87" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="56" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="B88" s="57" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="C88" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="56" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="B89" s="57" t="n">
+        <v>185.3</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="56" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="B90" s="57" t="n">
+        <v>183.9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="54" t="inlineStr">
+        <is>
+          <t>환율 · 위안</t>
+        </is>
+      </c>
+      <c r="B92" s="54" t="n"/>
+      <c r="C92" s="54" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B93" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C93" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="56" t="inlineStr">
+        <is>
+          <t>2Q25</t>
+        </is>
+      </c>
+      <c r="B94" s="57" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C94" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="56" t="inlineStr">
+        <is>
+          <t>1Q26</t>
+        </is>
+      </c>
+      <c r="B95" s="57" t="n">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="56" t="inlineStr">
+        <is>
+          <t>2Q26</t>
+        </is>
+      </c>
+      <c r="B96" s="57" t="n">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="54" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B98" s="54" t="n"/>
+      <c r="C98" s="54" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B99" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C99" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="56" t="inlineStr">
+        <is>
+          <t>jp</t>
+        </is>
+      </c>
+      <c r="B100" s="57" t="n">
+        <v>1164</v>
+      </c>
+      <c r="C100" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="56" t="inlineStr">
+        <is>
+          <t>ovs</t>
+        </is>
+      </c>
+      <c r="B101" s="57" t="n">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="56" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B102" s="57" t="n">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="56" t="inlineStr">
+        <is>
+          <t>fxs</t>
+        </is>
+      </c>
+      <c r="B103" s="57" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="56" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B104" s="57" t="n">
+        <v>3127</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="56" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B105" s="59" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="56" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B106" s="57" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="56" t="inlineStr">
+        <is>
+          <t>pre</t>
+        </is>
+      </c>
+      <c r="B107" s="57" t="n">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="56" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B108" s="57" t="n">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="56" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B109" s="57" t="n">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="54" t="inlineStr">
+        <is>
+          <t>EXQ 9031</t>
+        </is>
+      </c>
+      <c r="B111" s="54" t="n"/>
+      <c r="C111" s="54" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B112" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C112" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="56" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B113" s="57" t="n">
+        <v>2029.7</v>
+      </c>
+      <c r="C113" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="56" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B114" s="57" t="n">
+        <v>1875.9</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B115" s="57" t="n">
+        <v>2069.7</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B116" s="57" t="n">
+        <v>2443.7</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B117" s="57" t="n">
+        <v>2438.3</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B118" s="57" t="n">
+        <v>2349.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B119" s="57" t="n">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="B120" s="57" t="n">
+        <v>1851.7</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="B121" s="57" t="n">
+        <v>2221.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="B122" s="57" t="n">
+        <v>2579.7</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B123" s="57" t="n">
+        <v>2637.8</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="54" t="inlineStr">
+        <is>
+          <t>FANUC 매출</t>
+        </is>
+      </c>
+      <c r="B125" s="54" t="n"/>
+      <c r="C125" s="54" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="55" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B126" s="55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C126" s="55" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="56" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="B127" s="57" t="n">
+        <v>1969.24</v>
+      </c>
+      <c r="C127" s="58" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="56" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B128" s="57" t="n">
+        <v>1978.3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="56" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B129" s="57" t="n">
+        <v>1987.49</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B130" s="57" t="n">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B131" s="57" t="n">
+        <v>1928.62</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B132" s="57" t="n">
+        <v>1970.52</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="56" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B133" s="57" t="n">
+        <v>2121.15</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B134" s="57" t="n">
+        <v>1963.63</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q2</t>
+        </is>
+      </c>
+      <c r="B135" s="57" t="n">
+        <v>2112.05</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="B136" s="57" t="n">
+        <v>2157.44</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="56" t="inlineStr">
+        <is>
+          <t>2026-Q4</t>
+        </is>
+      </c>
+      <c r="B137" s="57" t="n">
+        <v>2345.19</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q1</t>
+        </is>
+      </c>
+      <c r="B138" s="57" t="n">
+        <v>2310.35</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="56" t="inlineStr">
+        <is>
+          <t>2027-Q2</t>
+        </is>
+      </c>
+      <c r="B139" s="57" t="n">
+        <v>2426.73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13804,17 +15410,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="60" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="60" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -13823,272 +15429,272 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2027년 3월 결산기 1분기 결산단신</t>
+          <t>2027년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120260717595564.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120261027557109.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 연간 결산단신</t>
+          <t>2027년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120260418506301.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120260717595564.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 3분기 결산단신</t>
+          <t>2026년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120260123537908.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120260418506301.pdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 2분기 결산단신</t>
+          <t>2026년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120251026578934.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120260123537908.pdf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026년 3월 결산기 1분기 결산단신</t>
+          <t>2026년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120250724520054.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120251026578934.pdf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 연간 결산단신</t>
+          <t>2026년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120250422520237.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120250724520054.pdf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 3분기 결산단신</t>
+          <t>2025년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120241218540581.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120250422520237.pdf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 2분기 결산단신</t>
+          <t>2025년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120241025503102.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120241218540581.pdf</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025년 3월 결산기 1분기 결산단신</t>
+          <t>2025년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120240724554357.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120241025503102.pdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 연간 결산단신</t>
+          <t>2025년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120240422574265.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120240724554357.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 3분기 결산단신</t>
+          <t>2024년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120240130522378.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120240422574265.pdf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 2분기 결산단신</t>
+          <t>2024년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120231022569679.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120240130522378.pdf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024년 3월 결산기 1분기 결산단신</t>
+          <t>2024년 3월 결산기 2분기 결산단신</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120230726527657.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120231022569679.pdf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 연간 결산단신</t>
+          <t>2024년 3월 결산기 1분기 결산단신</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120230422551105.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120230726527657.pdf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 3분기 결산단신</t>
+          <t>2023년 3월 결산기 연간 결산단신</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120230126594370.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120230422551105.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2022-10-28</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023년 3월 결산기 2분기 결산단신</t>
+          <t>2023년 3월 결산기 3분기 결산단신</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www2.jpx.co.jp/disc/68610/140120221024548369.pdf</t>
+          <t>https://www2.jpx.co.jp/disc/68610/140120230126594370.pdf</t>
         </is>
       </c>
     </row>
